--- a/data/PSBP_Master_Plant_Signage.xlsx
+++ b/data/PSBP_Master_Plant_Signage.xlsx
@@ -3420,7 +3420,7 @@
     <row r="11" ht="255.65" customHeight="1" s="58">
       <c r="A11" s="29" t="inlineStr">
         <is>
-          <t>Geiger tree</t>
+          <t>Geiger Tree</t>
         </is>
       </c>
       <c r="B11" s="29" t="inlineStr">
@@ -3563,7 +3563,6 @@
       <c r="Z11" s="33" t="inlineStr">
         <is>
           <t>Geiger Tree
-Scarlet Cordia
 Sebesten Plum (for fruit)</t>
         </is>
       </c>
@@ -3753,7 +3752,7 @@
     <row r="13" ht="255.65" customHeight="1" s="58">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t>Peacock Flower</t>
+          <t>Dwarf Poinciana</t>
         </is>
       </c>
       <c r="B13" s="29" t="inlineStr">
@@ -3893,7 +3892,7 @@
       </c>
       <c r="Z13" s="33" t="inlineStr">
         <is>
-          <t>Dwarf Poinciana
+          <t>Peacock Flower
 Pride of Barbados
 Flamboyant-de-Jardin
 Red Bird of Paradise</t>

--- a/data/PSBP_Master_Plant_Signage.xlsx
+++ b/data/PSBP_Master_Plant_Signage.xlsx
@@ -3562,8 +3562,7 @@
       </c>
       <c r="Z11" s="33" t="inlineStr">
         <is>
-          <t>Geiger Tree
-Sebesten Plum (for fruit)</t>
+          <t>Scarlet Cordia · Sebesten Plum (for fruit)</t>
         </is>
       </c>
       <c r="AA11" s="33" t="inlineStr">
@@ -4276,10 +4275,10 @@
       <c r="H16" s="32" t="n"/>
       <c r="I16" s="33" t="inlineStr">
         <is>
-          <t>The scarlet tubular flowers of Coral Bean are timed almost perfectly to coincide with the spring migration of Ruby-throated Hummingbirds moving north along the Gulf Coast — making this one of the most ecologically timed native plants in the park.
-The brilliant red seeds that follow are beautiful, familiar-looking, and seriously toxic.
-Thorny, deciduous, and tough enough to grow in pure sand and salt spray.
-A genuine Florida native that earns its keep for wildlife year-round.</t>
+          <t>The scarlet tubular flowers bloom in step with the spring migration of **Ruby-throated Hummingbirds** moving north along the Gulf Coast.
+The brilliant red seeds that follow are beautiful, familiar-looking, and **seriously toxic**.
+Thorny, deciduous, and tough enough to grow in pure sand and **salt spray**.
+A true **Florida native** that provides year-round value for wildlife.</t>
         </is>
       </c>
       <c r="J16" s="33" t="inlineStr">
@@ -4293,12 +4292,12 @@
 The seeds are among the most deceptively dangerous in Florida. They look like polished red beads — and have historically been used exactly that way, strung into jewelry and decorations across the Caribbean and Gulf South. They contain a suite of toxic alkaloids including erysopine, erythrinine, and hypaphorine, known to cause paralysis when ingested. In Mexico the seeds have been used as rat poison. Handle with gloves; keep away from children.
 Despite its toxicity, the Cherokee people used root decoctions medicinally for kidney and urinary conditions, and Florida Ethnobotany devotes two full pages to traditional uses of this plant across Indigenous cultures of the Southeast.
 The name herbacea — Latin for 'herbaceous' or 'low-growing' — was given because this species is more shrubby than the large tropical Erythrina trees common in South America and Africa, some of which reach 100 feet and are used as shade trees for coffee and cacao plantations. This is the modest North American representative of a globally significant genus.
-A member of the Fabaceae family — the same legume family as Sunshine Mimosa, Royal Poinciana, and Peacock Flower also in the park. The genus name Erythrina comes from the Greek erythros, meaning red — a reference to the flowers and seeds that define the plant.</t>
+A member of the Fabaceae family — the same legume family as Sunshine Mimosa, Royal Poinciana, and Dwarf Poinciana also in the park. The genus name Erythrina comes from the Greek erythros, meaning red — a reference to the flowers and seeds that define the plant.</t>
         </is>
       </c>
       <c r="L16" s="33" t="inlineStr">
         <is>
-          <t>The Coral Bean is one of the most hummingbird-focused native plants in Florida. Its long scarlet tubular flowers are shaped specifically for hummingbird bills and timed to coincide with Ruby-throated Hummingbird migration in spring — feeding northbound birds at a critical moment in their journey. Butterflies with longer tongues and bumblebees also work the flowers. The brilliant red seeds that follow are dispersed by birds that carry them from the split pods. The plant's thorny stems and dense branching habit make it an ideal refuge for small birds seeking protected roosting and nesting cover. The Erythrina borer moth (Terastia meticulosalis) uses it as a larval host — a less glamorous but ecologically real wildlife relationship.</t>
+          <t>The Coral Bean is one of the most hummingbird-focused native plants in Florida. Its long scarlet tubular flowers are shaped specifically for hummingbird bills and timed to coincide with Ruby-throated Hummingbird migration in spring — feeding northbound birds at a critical moment in their journey. Butterflies with longer tongues and bumblebees also work the flowers. The brilliant red seeds that follow are dispersed by birds that carry them from the split pods. The plant's thorny stems and dense branching habit make it an ideal refuge for small birds seeking protected roosting and nesting cover. The Erythrina borer moth (Terastia meticulosalis) uses it as a larval host.</t>
         </is>
       </c>
       <c r="M16" s="33" t="inlineStr">
@@ -4309,7 +4308,7 @@
 Seeds: Brilliant coral-red, polished-looking. TOXIC — contain multiple alkaloids causing paralysis. Handle with gloves.
 Leaves: Compound, with three deltoid (arrowhead-shaped) light green leaflets, each with tiny prickles along the underside of the margin. Stems armed with short curved spines.
 Bark: Smooth, light gray to whitish on mature stems.
-What to Look For: In spring, watch for vivid scarlet flower spikes appearing on nearly bare branches — and watch those branches for hummingbirds. In fall and winter, the split bean pods displaying brilliant red seeds against bare stems are unmistakable. Run a careful finger along a leaflet margin to feel the fine prickles — a reliable tactile ID feature.</t>
+What to Look For: In spring, watch for vivid scarlet flower spikes appearing on nearly bare branches — and watch those branches for hummingbirds. In fall and winter, the split bean pods displaying brilliant red seeds against bare stems are easy to spot. Run a careful finger along a leaflet margin to feel the fine prickles — a reliable tactile ID feature.</t>
         </is>
       </c>
       <c r="N16" s="33" t="inlineStr">

--- a/data/PSBP_Master_Plant_Signage.xlsx
+++ b/data/PSBP_Master_Plant_Signage.xlsx
@@ -4598,10 +4598,10 @@
       <c r="H18" s="32" t="n"/>
       <c r="I18" s="33" t="inlineStr">
         <is>
-          <t>The only palm native to both Florida and the Everglades system — you can tell a healthy Florida wetland by whether this palm is in it.
-It grows in dense clumping colonies that erupt from the water like small islands of green — one of the most iconic silhouettes in the Everglades.
-Its tolerance for periodic flooding is exceptional — it can stand in water for extended periods that would kill most palms.
-Not susceptible to lethal bronzing disease, which makes it a strong choice as that disease spreads through Florida.</t>
+          <t>An iconic native palm of the **Everglades** and South Florida wetlands — its presence is a living marker of healthy, wet native habitat.
+It grows in dense **clumping colonies** that erupt from the water like small islands of green — one of the most iconic silhouettes in the Everglades.
+Its tolerance for **periodic flooding** is exceptional — it can stand in water for extended periods that would kill most palms.
+Not susceptible to **lethal bronzing** disease, which makes it a strong choice as that disease spreads through Florida.</t>
         </is>
       </c>
       <c r="J18" s="33" t="inlineStr">
@@ -4629,7 +4629,7 @@
 Fruit: Quarter-inch round fruits passing through green and orange stages before turning black when ripe in fall.
 Leaves: Light green palmate (fan-shaped) blades about 2 feet across, silver underneath, on spiny petioles up to 3 feet long. The silver underside is a reliable field ID feature.
 Trunk: Multiple slender stems 2 to 3 inches in diameter, covered in fibrous burlap-like matting and old leaf bases, often with a reddish-brown coloring.
-What to Look For: The multi-stemmed clumping habit is unmistakable — no solitary trunk. Look for the silvery underside of the fronds catching the light. The dense mound form that erupts from wet ground is the defining silhouette. Watch for the orange-to-black fruit clusters in fall.</t>
+What to Look For: The multi-stemmed clumping habit is distinctive — no solitary trunk. Look for the silvery underside of the fronds catching the light. The dense mound form that erupts from wet ground is the defining silhouette. Watch for the orange-to-black fruit clusters in fall.</t>
         </is>
       </c>
       <c r="N18" s="33" t="inlineStr">
@@ -4707,7 +4707,11 @@
           <t>Everglades Palm · Madeira Palm</t>
         </is>
       </c>
-      <c r="AA18" s="33" t="n"/>
+      <c r="AA18" s="33" t="inlineStr">
+        <is>
+          <t>Keeping a Paurotis clump this size looking sharp is real work. At Palma Sola, one dedicated volunteer takes on the job — clearing the dense tangle of suckers and old growth at the base, then reaching high overhead with a long-pole pruner to cut away spent fronds. On a mature clump it's a full day's effort, sometimes two. Next time you pass a clean, well-shaped grove, you're looking at hours of careful hands-on care.</t>
+        </is>
+      </c>
       <c r="AB18" s="33" t="inlineStr">
         <is>
           <t>Native Palms and Cycads</t>
@@ -6663,10 +6667,10 @@
       <c r="H31" s="32" t="n"/>
       <c r="I31" s="33" t="inlineStr">
         <is>
-          <t>Fakahatchee Grass is in the same botanical subtribe as corn's wild ancestor — the two can hybridize. Its tiny seed spike looks strikingly similar to a miniature ear of early corn.
-The popped seeds of Fakahatchee Grass are reportedly almost indistinguishable from open-pollinated strawberry popcorn — a fact that has interested researchers studying corn's origins.
-It gets both its common names from the same place: the Fakahatchee Strand Preserve State Park in Collier County — one of Florida's most ecologically significant wild areas, about 150 miles south of our park.
-The dense fibrous root system is so effective at preventing erosion that it is actively used in restoration projects along stream banks and wet slopes.</t>
+          <t>Fakahatchee Grass shares a botanical subtribe with corn's wild ancestor, and the two can hybridize — its tiny seed spike looks like a miniature ear of **early corn**.
+The popped seeds are reportedly almost indistinguishable from open-pollinated **strawberry popcorn** — a quirk that has interested researchers studying corn's origins.
+Its name comes from the **Fakahatchee Strand** in Collier County, a biologically rich wetland about 150 miles south of Palma Sola.
+The dense fibrous root system is so good at preventing **erosion** that it's used in restoration projects along stream banks and wet slopes.</t>
         </is>
       </c>
       <c r="J31" s="33" t="inlineStr">
@@ -6678,7 +6682,7 @@
         <is>
           <t>The corn connection is genuine but requires precision to explain correctly. Modern corn (Zea mays) descended from Teosinte — a group of wild Mexican grasses — through roughly 10,000 years of Indigenous agricultural selection. Fakahatchee Grass (Tripsacum) and corn's Teosinte ancestors belong to the same botanical subtribe, Tripsacinae, and the two genera can hybridize experimentally. The seed spike of Tripsacum looks strikingly like a miniature primitive corn ear — complete with the stacked kernel structure of early cultivated varieties. Indigenous peoples in the Southeast knew Tripsacum well and likely observed the resemblance; the seeds have been found in archaeological sites, though how they were used is not fully documented.
 Researchers have noted that the popped kernels of Tripsacum dactyloides are almost indistinguishable from open-pollinated strawberry popcorn — adding a sensory dimension to the evolutionary story.
-The name Fakahatchee comes from the Mikasuki language — the strand it names in Collier County is one of Florida's most important wild orchid habitats and home to the only wild population of the Royal Palm in the US. This plant shares its name with one of Florida's finest wild places.
+The name Fakahatchee comes from the Mikasuki language — the strand it names in Collier County is one of Florida's most important wild orchid habitats and home to one of the largest wild populations of native Royal Palms (Roystonea regia) in the country.
 A note on this plant's category: Fakahatchee Grass appears in the 'Plants to Watch and Invasive Awareness' section not because it is invasive or listed by FISC, but because it spreads aggressively at Palma Sola beyond where it was originally planted. This is worth noting for park management even though it poses no ecological threat to natural areas outside the park. Florida native, not on any invasive species list.</t>
         </is>
       </c>
@@ -6773,7 +6777,7 @@
       </c>
       <c r="AA31" s="33" t="inlineStr">
         <is>
-          <t>NOMENCLATURE / RELATIONSHIP: Tripsacum belongs to the subtribe Tripsacinae alongside Zea (corn) and its wild ancestor teosinte; the genera can hybridize. Tripsacum is a very close relative of corn, not its direct ancestor.</t>
+          <t>Fakahatchee Grass is a tough customer. When we've needed to remove a clump at Palma Sola, the John Deere Gator isn't enough to budge it — it takes the full tractor to drag that dense, fibrous root mass out of the ground. The same root system that makes it a beast to move is exactly what makes it so good at holding soil in place.</t>
         </is>
       </c>
       <c r="AB31" s="33" t="inlineStr">
@@ -7790,10 +7794,10 @@
       <c r="H38" s="32" t="n"/>
       <c r="I38" s="33" t="inlineStr">
         <is>
-          <t>The Umbrella Tree earned its spot on Florida's invasive species watch list the hard way — birds eat the red berries and deposit seeds in hammocks, where seedlings establish quickly and can eventually strangle and overtop native trees.
-In summer, the canopy explodes with striking, three-foot-wide clusters of deep red flower spikes that spread out like the arms of an octopus.
-Originally from Queensland and New Guinea, it was widely planted as an ornamental before its invasive potential was recognized. The plant here is maintained as an educational specimen: knowing what to watch for in the wild matters. Its story is a useful reminder of how quickly an introduced species can escape cultivation.
-Palma Sola Botanical Garden has seen no invasive behavior with its specimen. We lost a prized specimen due to salt exposure from the hurricanes of 2024.</t>
+          <t>One of Florida's problem invaders: birds eat the red berries and drop the seeds in wild hammocks, where a seedling can take root high in a native tree and slowly **strangle** it.
+In summer the canopy puts out dramatic three-foot-wide clusters of deep red flower spikes that radiate like the arms of an **octopus**.
+Originally from Queensland and New Guinea, it was a wildly popular ornamental before its **invasive** potential was understood — the park keeps one as a teaching specimen for exactly that reason.
+Palma Sola once had two of these about twenty yards apart; the 2024 saltwater floods claimed one, and the **survivor** is steadily fighting its way back to life.</t>
         </is>
       </c>
       <c r="J38" s="33" t="inlineStr">
@@ -7803,9 +7807,9 @@
       </c>
       <c r="K38" s="33" t="inlineStr">
         <is>
-          <t>The Umbrella Tree's story is a cautionary tale in Florida horticulture. For years it was a staple landscape plant — easy, fast, dramatic, widely sold. Then ecologists began finding it in hammocks where no one had planted it. The mechanism was birds: the red berries are eagerly eaten and the seeds deposited intact in natural areas, sometimes miles away. Young Scheffleras start as epiphytes — germinating in the crotch of a native tree, sending roots down the bark — before eventually overtopping and strangling the host. By the time the problem was recognized, it was already established across South Florida's most sensitive hammock habitats. It is now a FISC Category I invasive, the highest designation, and IFAS classifies it as invasive in both Central and South Florida.
+          <t>The Umbrella Tree's story is a cautionary tale in Florida horticulture. For years it was a staple landscape plant — easy, fast, dramatic, widely sold. In fact, it remains one of the most common houseplants in North America — perfectly well-behaved in a pot up north, yet an aggressive invader in frost-free South Florida. Then ecologists began finding it in hammocks where no one had planted it. The mechanism was birds: the red berries are eagerly eaten and the seeds deposited intact in natural areas, sometimes miles away. Young Scheffleras start as epiphytes — germinating in the crotch of a native tree, sending roots down the bark — before eventually overtopping and strangling the host. By the time the problem was recognized, it was already established across South Florida's most sensitive hammock habitats. It is now a FISC Category I invasive, the highest designation, and IFAS classifies it as invasive in both Central and South Florida.
 Large established individuals (over 10 inches trunk diameter) are particularly difficult to eradicate — the recommended treatment is cut-stump application of Triclopyr, which can take up to 9 months to kill a large tree. The park's specimen is maintained as an educational display. It is worth keeping an eye on any volunteer seedlings in surrounding areas.
-Note: the current accepted scientific name is *Heptapleurum actinophyllum* — the genus was reclassified from Schefflera. Most literature and signage still uses Schefflera actinophylla.</t>
+Note: the current accepted scientific name is *Heptapleurum actinophyllum* — the genus was reclassified from Schefflera based on molecular (DNA) analysis showing it is distinct from the true Scheffleras. Most literature and signage still uses Schefflera actinophylla.</t>
         </is>
       </c>
       <c r="L38" s="33" t="inlineStr">
@@ -7816,7 +7820,7 @@
       <c r="M38" s="33" t="inlineStr">
         <is>
           <t>Produces flowers in summer when grown in full sun — an unusual radial arrangement of multiple flower spikes extending from a central point, resembling the legs of an octopus (one of its common names). Can start as an epiphyte, germinating in tree crotches before rooting to the ground.
-Flowers: Small, dark red, on the ends of 3-foot-diameter radiating clusters of stems — striking but easily overlooked.
+Flowers: Small and dark red, borne on radial clusters of stems up to three feet across.
 Fruit: Small, round, dark red to purple, produced prolifically. Highly attractive to birds — the primary dispersal vector.
 Leaves: Large, palmately compound with 7 to 16 glossy oval leaflets arranged in a circular pattern. Each leaflet up to 12 inches long.
 What to Look For: The circular arrangement of leaflets on long petioles creates the 'umbrella' silhouette the name describes — look up into the crown from below for the full effect. The octopus-like flower stalks in summer are distinctive. Watch for volunteer seedlings — small umbrella-leaved plants appearing in unexpected locations.</t>
@@ -7890,10 +7894,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z38" s="37" t="n"/>
+      <c r="Z38" s="37" t="inlineStr">
+        <is>
+          <t>Octopus Tree · Queensland Umbrella Tree · Australian Umbrella Tree</t>
+        </is>
+      </c>
       <c r="AA38" s="33" t="inlineStr">
         <is>
-          <t>NOMENCLATURE: The accepted genus name has been revised to Heptapleurum actinophyllum, though most literature and signage still uses Schefflera actinophylla. Family on signage: Araliaceae (the ivy and ginseng family).</t>
+          <t>In its years at Palma Sola — in the park's particular microclimate — this species has shown no sign of the invasive behavior it's known for elsewhere. We keep a close watch for volunteer seedlings all the same, and never propagate or plant it elsewhere on the property.</t>
         </is>
       </c>
       <c r="AB38" s="33" t="inlineStr">
@@ -8608,10 +8616,10 @@
       <c r="H43" s="32" t="n"/>
       <c r="I43" s="33" t="inlineStr">
         <is>
-          <t>The flower spike coils like a scorpion's tail and slowly uncurls as each tiny white bloom opens in turn, from base to tip.
-It's a Florida native and a year-round butterfly magnet — its nectar feeds the Miami blue, Schaus' swallowtail, gulf fritillary, queen, and a long list of others.
-Palma Sola is planting it aggressively along pond shores as part of two estuary-program restoration grants — it was chosen by UF/IFAS consultants for stabilizing brackish shorelines.
-The genus name Heliotropium means 'sun-turning,' from the old belief that the flowers follow the sun across the sky.</t>
+          <t>The flower spike coils like a **scorpion's tail** and slowly uncurls as each tiny white bloom opens in turn, from base to tip.
+It's a Florida native and a year-round **butterfly magnet** — its nectar feeds the Miami blue, Schaus' swallowtail, gulf fritillary, queen, and a long list of others.
+It's one of several UF/IFAS-recommended natives Palma Sola is planting along its pond shores for **erosion control** — look for it around most of the park's pond banks.
+The genus name Heliotropium means '**sun-turning**,' from the old belief that the flowers follow the sun across the sky.</t>
         </is>
       </c>
       <c r="J43" s="33" t="inlineStr">
@@ -8622,7 +8630,7 @@
       <c r="K43" s="33" t="inlineStr">
         <is>
           <t>The Scorpion Tail's coiled flowering spike is a small marvel of plant engineering. Botanists call it a scorpioid cyme (or cincinnus): the flower axis curls over on itself, and the blossoms open in sequence from the base of the coil toward the tip, so the spike appears to slowly unfurl over days. The common name captures it exactly, and the genus name reaches even further back — Heliotropium comes from the Greek helios ('sun') and trepein ('to turn'), from the old belief that these plants turn their flowers to follow the sun.
-At Palma Sola, this modest native has become a workhorse of restoration. The park is deploying it aggressively along its pond shorelines under two complementary grants — from the Tampa Bay Estuary Program and the Sarasota Bay Estuary Program — to restore and stabilize pond edges. UF/IFAS consultants selected it as one of the species that perform well for shoreline stabilization in brackish water, where many ornamentals fail. A plant most people walk past as a roadside weed is, in this setting, doing real ecological work holding the park's shorelines together — and feeding an exceptional range of butterflies while it does (see Wildlife Value).
+At Palma Sola, this modest native has become a workhorse of restoration. The park is deploying it aggressively along its pond shorelines under two complementary grants — from the Tampa Bay Estuary Program and the Sarasota Bay Estuary Program — to restore and stabilize pond edges. UF/IFAS consultants selected it as one of several species that perform well for shoreline stabilization in brackish water, where many ornamentals fail. A plant most people walk past as a roadside weed is, in this setting, doing real ecological work holding the park's shorelines together — and feeding an exceptional range of butterflies while it does (see Wildlife Value).
 A note of caution balances the charm: like many in its family, Scorpion Tail contains pyrrolizidine alkaloids, compounds that can harm the liver if the plant is eaten in quantity. It has a history of folk-medicinal use in the Caribbean, but it is not a plant to eat or self-medicate with.</t>
         </is>
       </c>
@@ -8638,7 +8646,7 @@
 Fruit: Small dry fruit splitting into seed-bearing nutlets; seeds favored by birds.
 Leaves: Lanceolate to elliptic, alternate, stalked, with deeply veined surfaces and softly hairy undersides.
 Stems: Branched, herbaceous to slightly woody, sprawling to upright.
-What to Look For: Look for the distinctive coiled flower spike — the namesake scorpion's tail — slowly unfurling as the little white flowers open along it. Watch the blooms for butterfly traffic; this is one of the park's busiest nectar stops. Along the pond shorelines, notice it planted in quantity as part of the restoration work, knitting the water's edge together.</t>
+What to Look For: Look for the distinctive coiled flower spike — the namesake scorpion's tail — slowly unfurling as the little white flowers open along it. Watch the blooms for butterfly traffic; this is one of the park's busiest nectar stops. Around most of the park's pond banks, notice it planted in quantity alongside other native shoreline species, knitting the water's edge together.</t>
         </is>
       </c>
       <c r="N43" s="33" t="inlineStr">
@@ -8662,7 +8670,7 @@
       </c>
       <c r="P43" s="35" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Q43" s="33" t="inlineStr">
@@ -8715,11 +8723,7 @@
           <t>Scorpionstail · Scorpion's Tail · Butterfly Heliotrope</t>
         </is>
       </c>
-      <c r="AA43" s="33" t="inlineStr">
-        <is>
-          <t>PARK CONTEXT: Being deployed aggressively around the park for pond/shoreline restoration under two complementary grants — Tampa Bay Estuary Program and Sarasota Bay Estuary Program. Selected (among several species) by UF/IFAS consultants as effective for shore stabilization along brackish water. TAXONOMY NOTE: Some authorities (e.g., Wikipedia) now place this in family Heliotropiaceae, segregated from Boraginaceae. Sheet keeps Boraginaceae to match FNPS / FL Wildflower Foundation usage and the park's Geiger Tree; revisit if standardizing on the newer split.</t>
-        </is>
-      </c>
+      <c r="AA43" s="33" t="n"/>
       <c r="AB43" s="33" t="inlineStr">
         <is>
           <t>Native Groundcovers and Wildflowers</t>
@@ -9452,12 +9456,11 @@
       </c>
       <c r="M48" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Spores — No flowers, fruit, or seeds. Reproduction by microscopic spores released from sori: fuzzy, felt-like brown patches that form on the undersides of fertile frond tips.
-Vegetative spread — The colony expands by producing small offset plants at the edges of the shield fronds. These can be detached and mounted on a new surface.
-Shield fronds — Round, flat, papery, brown. Clasp the host surface, protect the root mass, trap organic debris. Do not photosynthesize.
-Fertile fronds — Arching, grey-green, deeply forked. The antler-shaped fronds visible from a distance. Carry the sori.
-Brown fertile fronds — Not dead. Covered in spores on undersides. Leave them.
+          <t>Spores: No flowers, fruit, or seeds. Reproduction by microscopic spores released from sori: fuzzy, felt-like brown patches that form on the undersides of fertile frond tips.
+Vegetative spread: The colony expands by producing small offset plants at the edges of the shield fronds. These can be detached and mounted on a new surface.
+Shield fronds: Round, flat, papery, brown. Clasp the host surface, protect the root mass, trap organic debris. Do not photosynthesize.
+Fertile fronds: Arching, grey-green, deeply forked. The antler-shaped fronds visible from a distance. Carry the sori.
+Brown fertile fronds: Not dead. Covered in spores on undersides. Leave them.
 What to Look For: The forked antler fronds are the obvious first feature. Look deeper into the base for the flat overlapping brown shield fronds gripping the palm trunk. Turn a fertile frond tip over to check for sori.</t>
         </is>
       </c>
@@ -9687,7 +9690,7 @@
     <row r="50" ht="167.65" customHeight="1" s="58">
       <c r="A50" s="29" t="inlineStr">
         <is>
-          <t>Spath Lily</t>
+          <t>Peace Lily</t>
         </is>
       </c>
       <c r="B50" s="29" t="inlineStr">
@@ -9723,10 +9726,10 @@
       <c r="H50" s="32" t="n"/>
       <c r="I50" s="33" t="inlineStr">
         <is>
-          <t>Not a true lily — the name is a coincidence of appearance. It belongs to the aroid family, alongside philodendrons, anthuriums, and the park's own Xanadu.
-The white flag-shaped bloom is not a petal. It is a spathe — a modified leaf — wrapped around a spike of tiny true flowers called the spadix.
-In the wild, the spadix generates heat at night and releases scent to attract beetle pollinators. Cultivated varieties have largely lost the scent.
-Sitting quietly at the base of the office walkway, these plants are easy to overlook — especially with the staghorn fern suspended in the fig tree just above them.</t>
+          <t>Not a **true lily** — the name is a coincidence of appearance. It belongs to the aroid family, alongside philodendrons, anthuriums, and the park's own Xanadu.
+The white flag-shaped bloom is not a petal. It is a **spathe** — a modified leaf — wrapped around a spike of tiny true flowers called the spadix.
+In the wild, the spadix **generates heat** at night and releases scent to attract beetle pollinators; cultivated varieties have largely lost the scent.
+Tucked into a quiet, shady footpath by the office, these plants are easy to miss — especially under the big **staghorn fern** hanging in the fig tree just above them.</t>
         </is>
       </c>
       <c r="J50" s="33" t="inlineStr">
@@ -9736,7 +9739,7 @@
       </c>
       <c r="K50" s="33" t="inlineStr">
         <is>
-          <t>Like the Snake Plant, the Peace Lily was included in NASA's Clean Air Study as effective at removing indoor air pollutants including ammonia, benzene, formaldehyde, and trichloroethylene. It remains one of the few genuinely research-backed air-cleaning houseplants. In the language of flowers white flowers generally represent peace, purity, and sympathy — which is why Peace Lilies are commonly given at funerals. The spathe is technically not a petal but a modified leaf — the actual flowers are tiny and clustered on the spadix inside it.</t>
+          <t>Like the Snake Plant, the Peace Lily was one of the plants in NASA's 1989 Clean Air Study, which found it absorbed pollutants like benzene and formaldehyde in sealed test chambers. Later research, though, showed houseplants do little for the air in a real room — the popular 'air-purifying' claim outran the science. In the language of flowers white flowers generally represent peace, purity, and sympathy — which is why Peace Lilies are commonly given at funerals. The spathe is technically not a petal but a modified leaf — the actual flowers are tiny and clustered on the spadix inside it.</t>
         </is>
       </c>
       <c r="L50" s="37" t="inlineStr">
@@ -9811,7 +9814,7 @@
       </c>
       <c r="Z50" s="33" t="inlineStr">
         <is>
-          <t>Peace Lily</t>
+          <t>Spath Lily</t>
         </is>
       </c>
       <c r="AA50" s="33" t="n"/>
@@ -9865,20 +9868,20 @@
       <c r="H51" s="32" t="n"/>
       <c r="I51" s="33" t="inlineStr">
         <is>
-          <t>The drooping red flower spikes — up to 18 inches long, soft as velvet — are entirely composed of tiny individual flowers with no petals at all; the color comes from massed red stamens.
-Native to the Pacific Islands and Southeast Asia, it's been cultivated as an ornamental for so long that its wild progenitor is difficult to identify.
-The name 'Chenille' comes from the French word for caterpillar, which the flower spikes resemble.
-Hummingbirds probe the hanging spikes for nectar.</t>
+          <t>The velvety red spikes — up to 18 inches long — have **no petals** at all; their color comes from masses of tiny red female flowers.
+Native to Southeast Asia and New Guinea, it's been grown as an ornamental so long that its **wild ancestor** is hard to pin down.
+The name 'Chenille' is French for **caterpillar** — which the fuzzy hanging spikes resemble.
+Every Chenille Plant in the nursery trade is **female** — the species is dioecious, and the plain-flowered males were never brought into cultivation.</t>
         </is>
       </c>
       <c r="J51" s="33" t="inlineStr">
         <is>
-          <t>Native to Southeast Asia, particularly Malaysia and New Guinea. A member of the Euphorbiaceae family — same family as the Copperleaf (Java White), Peregrina, and Pencil Tree also in the park. The common name Chenille comes from the French word for "caterpillar" — the long drooping red flower spikes resemble caterpillars or the looped chenille fabric used in upholstery.</t>
+          <t>Native to Southeast Asia, particularly Malaysia and New Guinea. A member of the Euphorbiaceae family — the same family as the Copperleaf, Peregrina, and Pencil Tree also in the park.</t>
         </is>
       </c>
       <c r="K51" s="33" t="inlineStr">
         <is>
-          <t>Every Chenille Plant sold in nurseries worldwide is female. The male plants exist in the wild but have never been introduced to horticulture because their flowers are inconspicuous and no one wanted them. The female's extravagant drooping red flower spikes — up to 18 inches long — are one of the most dramatic flower forms available for Florida tropical gardens. The Euphorbiaceae family contains some of the plant world's most extreme diversity — from tiny annual weeds to massive trees, from cacti-like succulents to the rubber tree — all linked by their milky latex sap.</t>
+          <t>Every Chenille Plant sold in nurseries worldwide is female. The male plants exist in the wild but were never brought into horticulture — their flowers are inconspicuous, so no one wanted them. The flowers are also apetalous (petal-less): instead of bright petals, the plant packs its display into masses of fine red styles, forming those velvety 18-inch spikes — one of the most dramatic flower forms grown in Florida tropical gardens. The Euphorbiaceae family spans extraordinary diversity — from tiny weeds to massive trees, from cactus-like succulents to the rubber tree — many sharing a milky latex sap.</t>
         </is>
       </c>
       <c r="L51" s="37" t="inlineStr">
@@ -9953,7 +9956,7 @@
       </c>
       <c r="Z51" s="33" t="inlineStr">
         <is>
-          <t>Love-Lies-Bleeding</t>
+          <t>Red Hot Cat's Tail · Foxtail · Philippine Medusa</t>
         </is>
       </c>
       <c r="AA51" s="33" t="n"/>
@@ -10039,11 +10042,10 @@
       </c>
       <c r="M52" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Appear in spring, on bare leafless branches before or as new leaves emerge. Each flower is approximately 6 inches across with roughly 400 long, slender stamens — white in the var. album form. The shaving-brush resemblance is exact and unmistakable. Pollinated primarily by bats and moths at night; bees and hummingbirds visit by day.
-Fruit and Seeds — Seed pods produce kapok-like cottony white fiber. When pods split, the floss carries seeds on the wind.
-Leaves — New leaves emerge bright red and mature to green. Palmately compound, with 5–7 leaflets. The tree is fully deciduous — bare during the dry winter season and during flowering.
-Trunk — Gray-green, with distinctive swelling at the base that stores water. Striped with greens, yellows, browns, and white in the wood grain. Young specimens have a dramatically swollen, melon-like caudex.
+          <t>Flowers: Appear in spring, on bare leafless branches before or as new leaves emerge. Each flower is approximately 6 inches across with roughly 400 long, slender stamens — white in the var. album form. The shaving-brush resemblance is exact and unmistakable. Pollinated primarily by bats and moths at night; bees and hummingbirds visit by day.
+Fruit and Seeds: Seed pods produce kapok-like cottony white fiber. When pods split, the floss carries seeds on the wind.
+Leaves: New leaves emerge bright red and mature to green. Palmately compound, with 5–7 leaflets. The tree is fully deciduous — bare during the dry winter season and during flowering.
+Trunk: Gray-green, with distinctive swelling at the base that stores water. Striped with greens, yellows, browns, and white in the wood grain. Young specimens have a dramatically swollen, melon-like caudex.
 What to Look For: The bare-branch flowering in spring is the signature event — large white brush-like flowers on naked branches are visible from some distance. Year-round, the swollen gray-green trunk base and palmately compound leaves identify the tree. New red foliage in spring is a secondary marker.</t>
         </is>
       </c>
@@ -10191,11 +10193,10 @@
       </c>
       <c r="M53" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Orange to orange-red composite daisy-like blooms about 1 inch across, in clusters at branch tips. Each apparent flower is actually dozens of tiny florets. Blooms nearly year-round in Florida, with heaviest flowering in autumn and winter. Flowers age from orange to red as they mature.
-Fruit and Seeds — Small ribbed seed heads with persistent bristles forming dandelion-like puffs. Wind-dispersed and viable for a short window after release. Stem cuttings also root readily.
-Leaves — Thick, deep green, arrowhead-shaped, 2 to 4 inches long and slightly fleshy. Evergreen.
-Vine habit — Fast-growing twining climber, slightly woody with age. Reaches 16 to 33 feet. Climbs fences, trellises, and structures quickly and densely.
+          <t>Flowers: Orange to orange-red composite daisy-like blooms about 1 inch across, in clusters at branch tips. Each apparent flower is actually dozens of tiny florets. Blooms nearly year-round in Florida, with heaviest flowering in autumn and winter. Flowers age from orange to red as they mature.
+Fruit and Seeds: Small ribbed seed heads with persistent bristles forming dandelion-like puffs. Wind-dispersed and viable for a short window after release. Stem cuttings also root readily.
+Leaves: Thick, deep green, arrowhead-shaped, 2 to 4 inches long and slightly fleshy. Evergreen.
+Vine habit: Fast-growing twining climber, slightly woody with age. Reaches 16 to 33 feet. Climbs fences, trellises, and structures quickly and densely.
 What to Look For: At the park, look up — the vine lives on top of the nursery fence and greenhouse structure, not at eye level. The orange flower clusters are visible from a distance when in bloom. Follow the path past the banana trees to get underneath it.</t>
         </is>
       </c>
@@ -10343,11 +10344,10 @@
       </c>
       <c r="M54" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Dense 3-inch clusters of star-shaped tubular flowers at branch tips, each with exactly five petals. Available in red, pink, lavender, and white; red selections are most attractive to hummingbirds. Blooms nearly year-round in Central and South Florida.
-Fruit and Seeds — Small inconspicuous capsules. Propagates readily from stem cuttings; also from seed.
-Leaves — Lance-shaped, covered with fine hairs on both surfaces, with prominent veins on the undersides. Medium green. Leaves are the source of the species name lanceolata — lance-leaved.
-Form — Upright evergreen shrub or tall perennial, 2 to 4 feet tall, moderately fast growing.
+          <t>Flowers: Dense 3-inch clusters of star-shaped tubular flowers at branch tips, each with exactly five petals. Available in red, pink, lavender, and white; red selections are most attractive to hummingbirds. Blooms nearly year-round in Central and South Florida.
+Fruit and Seeds: Small inconspicuous capsules. Propagates readily from stem cuttings; also from seed.
+Leaves: Lance-shaped, covered with fine hairs on both surfaces, with prominent veins on the undersides. Medium green. Leaves are the source of the species name lanceolata — lance-leaved.
+Form: Upright evergreen shrub or tall perennial, 2 to 4 feet tall, moderately fast growing.
 What to Look For: The five-pointed star shape of each individual flower is distinctive up close — count the petals and you will always find five. The clustered flower heads at branch tips are visible from a distance. Fine leaf hairs give the foliage a slightly soft texture.</t>
         </is>
       </c>
@@ -10496,11 +10496,10 @@
       </c>
       <c r="M55" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Greenish-white, small, produced on erect spikes up to 60 cm long. Not ornamentally significant. The tree is dioecious — male and female flowers on separate plants; only female trees produce fruit.
-Fruit — Small, approximately 2 cm in diameter, in grape-like clusters. Edible on related species; similarly edible here though not widely consumed. Eaten by birds.
-Leaves — The defining feature. Orbicular (round), extremely variable in size from small to up to 90 cm (3 feet) in diameter. Bright green above, paler below with yellow to reddish veins. Smooth wavy margin. Stiff and heavy — a large fallen leaf has real weight to it. Juvenile plants produce larger leaves than mature ones.
-Trunk — Upright, can grow to 2 feet or more in diameter. Open, sparsely branched crown.
+          <t>Flowers: Greenish-white, small, produced on erect spikes up to 60 cm long. Not ornamentally significant. The tree is dioecious — male and female flowers on separate plants; only female trees produce fruit.
+Fruit: Small, approximately 2 cm in diameter, in grape-like clusters. Edible on related species; similarly edible here though not widely consumed. Eaten by birds.
+Leaves: The defining feature. Orbicular (round), extremely variable in size from small to up to 90 cm (3 feet) in diameter. Bright green above, paler below with yellow to reddish veins. Smooth wavy margin. Stiff and heavy — a large fallen leaf has real weight to it. Juvenile plants produce larger leaves than mature ones.
+Trunk: Upright, can grow to 2 feet or more in diameter. Open, sparsely branched crown.
 What to Look For: The leaves are unmistakable — no other tree in the park or in most Florida gardens produces a round leaf anywhere near this size. Look for the yellow-red vein pattern on the underside. Fallen leaves on the ground around the tree are often as interesting as those still attached.</t>
         </is>
       </c>
@@ -10649,11 +10648,10 @@
       </c>
       <c r="M56" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Orange-pink, hibiscus-like, five petals with a prominent central staminal column typical of the mallow family. Bloom period: late winter to early spring, roughly February through May. Visited by hummingbirds and native bees.
-Fruit and Seeds — Small capsule fruits containing seeds. Reseeds readily — short-lived as individual plants but self-maintaining as a colony. Easily grown from seed.
-Leaves — Maple-like, lobed, covered in fine soft hairs. Medium texture. Alternate arrangement.
-Form — Upright, loosely branching shrub to 7 feet. Stems are softly woody rather than truly woody. Tends toward a rangy, open habit unless periodically cut back.
+          <t>Flowers: Orange-pink, hibiscus-like, five petals with a prominent central staminal column typical of the mallow family. Bloom period: late winter to early spring, roughly February through May. Visited by hummingbirds and native bees.
+Fruit and Seeds: Small capsule fruits containing seeds. Reseeds readily — short-lived as individual plants but self-maintaining as a colony. Easily grown from seed.
+Leaves: Maple-like, lobed, covered in fine soft hairs. Medium texture. Alternate arrangement.
+Form: Upright, loosely branching shrub to 7 feet. Stems are softly woody rather than truly woody. Tends toward a rangy, open habit unless periodically cut back.
 What to Look For: Along the pond bank to the left of the native Cannas. The open habit and soft hairy leaves are visible year-round. In late winter, watch for the orange-pink flowers — five petals, central staminal column, the unmistakable mallow family signature.</t>
         </is>
       </c>
@@ -10797,12 +10795,11 @@
       </c>
       <c r="M57" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Bracts — The orange structures are modified leaves called bracts, arranged alternately on the flower stalk. Waxy, waterproof, and long-lasting — weeks after the true flowers inside have finished, the bracts remain colorful. Excellent as cut flowers.
-Flowers — Small, inconspicuous, tucked inside the bracts. Cream to yellow with darker tips. Produce abundant nectar.
-Leaves — Large, lanceolate, bright deep green with a prominent central vein. Resemble banana leaves. Can shred along the veins in strong wind.
-Rhizomes — The plant spreads by underground rhizomes extending outward from the planting over time. Thinner than canna rhizomes — a useful distinction when digging both out of the same bed.
-Propagation — Division of rhizomes. Each section with a growing point establishes a new plant.
+          <t>Bracts: The orange structures are modified leaves called bracts, arranged alternately on the flower stalk. Waxy, waterproof, and long-lasting — weeks after the true flowers inside have finished, the bracts remain colorful. Excellent as cut flowers.
+Flowers: Small, inconspicuous, tucked inside the bracts. Cream to yellow with darker tips. Produce abundant nectar.
+Leaves: Large, lanceolate, bright deep green with a prominent central vein. Resemble banana leaves. Can shred along the veins in strong wind.
+Rhizomes: The plant spreads by underground rhizomes extending outward from the planting over time. Thinner than canna rhizomes — a useful distinction when digging both out of the same bed.
+Propagation: Division of rhizomes. Each section with a growing point establishes a new plant.
 What to Look For: The orange boat-shaped bracts on an upright stalk above large banana-like leaves are unmistakable. Look inside a bract for the small true flowers. Where heliconia and canna grow together, compare the bract structure against the open canna flower clusters, and check rhizome thickness to tell them apart.</t>
         </is>
       </c>
@@ -10950,11 +10947,10 @@
       </c>
       <c r="M58" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Inconspicuous, in small catkins in spring. Dioecious — male and female flowers on separate plants. Female plants produce fruit; at least one male plant nearby is needed for pollination.
-Fruit — Small waxy gray-blue berries in clusters, ripening late summer to early fall. The waxy coating is aromatic and historically used for candle-making. Critically important as winter wildlife food.
-Leaves — Small, narrow, olive-green, aromatic when crushed. Evergreen. Slightly leathery.
-Form — Multi-trunked shrub to small tree, typically 10 to 15 feet tall and 8 to 10 feet wide, occasionally to 20 feet. Smooth light gray bark on multiple twisted trunks. Fast-growing. Spreads by root suckers to form colonies.
+          <t>Flowers: Inconspicuous, in small catkins in spring. Dioecious — male and female flowers on separate plants. Female plants produce fruit; at least one male plant nearby is needed for pollination.
+Fruit: Small waxy gray-blue berries in clusters, ripening late summer to early fall. The waxy coating is aromatic and historically used for candle-making. Critically important as winter wildlife food.
+Leaves: Small, narrow, olive-green, aromatic when crushed. Evergreen. Slightly leathery.
+Form: Multi-trunked shrub to small tree, typically 10 to 15 feet tall and 8 to 10 feet wide, occasionally to 20 feet. Smooth light gray bark on multiple twisted trunks. Fast-growing. Spreads by root suckers to form colonies.
 What to Look For: Along the far side of the cypress pond. The narrow olive-green aromatic leaves and smooth gray multi-stemmed trunks are the year-round markers. In late summer and fall, clusters of small gray waxy berries on female plants. Crush a leaf to release the distinctive bayberry fragrance.</t>
         </is>
       </c>
@@ -11078,10 +11074,10 @@
       <c r="H59" s="32" t="n"/>
       <c r="I59" s="33" t="inlineStr">
         <is>
-          <t>The largest fern in Florida, and found only in Florida among the 50 states — its cold sensitivity limits it to the peninsula and the Keys.
-Fronds can reach 12 feet. The plant grows two distinct frond types: sterile fronds are green, fertile fronds are covered in brown spores on the underside and have a leathery, weathered appearance. The fertile ones are what prompt people to want to tidy them up.
-The root and rhizome system is doing serious erosion work along the pond banks. The plant asks nothing in return and tolerates flooding that would kill most things.
-Three specimens at the park: two in the front pond, one in the cypress pond. None have reproduced in six years of observation.</t>
+          <t>The largest fern in Florida, and found **only in Florida** among the 50 states — its cold sensitivity limits it to the peninsula and the Keys.
+Fronds can reach **12 feet**. The plant grows two distinct frond types: sterile fronds are green, fertile fronds are covered in brown spores on the underside and have a leathery, weathered appearance.
+The root and rhizome system is doing serious **erosion** work along the pond banks. The plant asks nothing in return and tolerates flooding that would kill most things.
+**Three specimens** at the park: two in the front pond, one in the cypress pond. None have reproduced in six years of observation.</t>
         </is>
       </c>
       <c r="J59" s="33" t="inlineStr">
@@ -11092,7 +11088,7 @@
       <c r="K59" s="33" t="inlineStr">
         <is>
           <t>Three Giant Leather Ferns anchor the park ponds — two in the front pond, one in the cypress pond. They are formidable plants in both size and function, leaning out over the water and holding the bank with a network of rhizomes that resists erosion effectively. In six years of observation, none have reproduced.
-People regularly want to clean them up. The fertile fronds, covered in brown spores on their undersides, look weathered compared to the clean green sterile fronds, and the temptation to trim the brown sections is understandable. The practical problem is access. The plants lean away from the bank over the water. Getting to them means getting in the pond, knee-deep, with a plant that is several feet taller than you are. The correct management decision is to leave them alone, and they seem to understand this.
+People regularly want to clean them up. The fertile fronds, covered in brown spores on their undersides, look weathered compared to the clean green sterile fronds, and the temptation to trim the brown sections is understandable. But that brown, velvety layer isn't decay or disease — it's a dense carpet of sporangia, the plant's spore-producing structures, and a single fertile frond can release millions of microscopic spores. The practical problem is access. The plants lean away from the bank over the water. Getting to them means getting in the pond, knee-deep, with a plant that is several feet taller than you are. The correct management decision is to leave them alone.
 As a Florida-only fern — cold sensitivity keeps it out of every other state — it represents a genuinely regional plant. It tolerates brackish conditions well enough to grow at mangrove edges, which is unusual for a fern. The thick waxy frond texture that gives it its name is an adaptation to those conditions.
 They are self-maintaining. They do not need the park. The park needs them.</t>
         </is>
@@ -11106,11 +11102,10 @@
       </c>
       <c r="M59" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Spores — No flowers, no seeds. Reproduces by spores carried on the undersides of fertile fronds. Spores are distributed uniformly across the entire underside of fertile fronds rather than in discrete clusters — this acrostichoid pattern is a defining family characteristic.
-Frond types — Two distinct types on the same plant. Sterile fronds are green with smooth leaflets. Fertile fronds have brown, leathery undersides covered in spores — the source of both the common name and the urge to tidy them up. Both types are normal and healthy.
-Rhizomes — Spreads by underground rhizomes forming large clumping colonies. Root system is strong and specifically adapted for shoreline stabilization.
-Size — Fronds 6 to 12 feet long in ideal conditions. Plant spread 5 to 10 feet wide. One of the largest ferns in North America.
+          <t>Spores: No flowers, no seeds. Reproduces by spores carried on the undersides of fertile fronds. Spores are distributed uniformly across the entire underside of fertile fronds rather than in discrete clusters — this acrostichoid pattern is a defining family characteristic.
+Frond types: Two distinct types on the same plant. Sterile fronds are green with smooth leaflets. Fertile fronds have brown, leathery undersides covered in spores — the source of both the common name and the urge to tidy them up. Both types are normal and healthy.
+Rhizomes: Spreads by underground rhizomes forming large clumping colonies. Root system is strong and specifically adapted for shoreline stabilization.
+Size: Fronds 6 to 12 feet long in ideal conditions. Plant spread 5 to 10 feet wide. One of the largest ferns in North America.
 What to Look For: The sheer scale is the first thing — no other fern at the park approaches this size. Look for the two frond types side by side: green sterile fronds and brown leathery fertile fronds. The plants lean over the water from the pond banks; the best view is from across the pond.</t>
         </is>
       </c>
@@ -11174,7 +11169,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z59" s="37" t="n"/>
+      <c r="Z59" s="37" t="inlineStr">
+        <is>
+          <t>Inland Leather Fern</t>
+        </is>
+      </c>
       <c r="AA59" s="37" t="n"/>
       <c r="AB59" s="33" t="inlineStr">
         <is>
@@ -11254,11 +11253,10 @@
       </c>
       <c r="M60" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Small, tubular, pink to lavender, appearing in clusters at leaf nodes in summer. Inconspicuous individually but plentiful. Attract bees and native pollinators.
-Fruit — Dense clusters of brilliant magenta-purple berries encircling the stems at leaf nodes. Appear in late summer, persist through fall and into winter. A rarer white-berried variety (var. lactea) exists but is uncommon.
-Leaves — Opposite, ovate to elliptic with finely toothed margins. Light green, rough-textured, slightly fuzzy. Aromatic when crushed — releasing callicarpenal, a mosquito repellent compound. Stems are square in cross-section, the mint family signature.
-Form — Arching, multi-stemmed shrub, 3 to 8 feet tall and wide. Fast-growing. Deciduous, though in South Florida may retain leaves year-round.
+          <t>Flowers: Small, tubular, pink to lavender, appearing in clusters at leaf nodes in summer. Inconspicuous individually but plentiful. Attract bees and native pollinators.
+Fruit: Dense clusters of brilliant magenta-purple berries encircling the stems at leaf nodes. Appear in late summer, persist through fall and into winter. A rarer white-berried variety (var. lactea) exists but is uncommon.
+Leaves: Opposite, ovate to elliptic with finely toothed margins. Light green, rough-textured, slightly fuzzy. Aromatic when crushed — releasing callicarpenal, a mosquito repellent compound. Stems are square in cross-section, the mint family signature.
+Form: Arching, multi-stemmed shrub, 3 to 8 feet tall and wide. Fast-growing. Deciduous, though in South Florida may retain leaves year-round.
 What to Look For: The berry clusters in fall are unmistakable — dense magenta-purple encircling the stems at regular intervals. Crush a leaf to confirm with the aromatic scent. Square stems are a reliable year-round ID feature shared with all mint family members.</t>
         </is>
       </c>
@@ -11406,11 +11404,10 @@
       </c>
       <c r="M61" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — White to pale pink, appearing on bare branches in late winter before leaf flush. Open at night and close by midday. Pungent scent attracts bats and moths. Not ornamentally showy but an important ecological event.
-Fruit and Seeds — Ellipsoid woody capsules 3 to 6 inches long. Each contains up to 200 seeds embedded in silky kapok fiber. A single tree can produce up to 4,000 pods per season. Fiber is hollow, buoyant, and water-resistant.
-Leaves — Palmate compound, with 5 to 9 long narrow leaflets radiating from a central point. Deciduous — drops leaves during dry season, which is when flowering occurs.
-Trunk — Massive, buttressed at the base with wide spreading roots. Large conical spines on trunk and major branches. Horizontal branching creates a distinctive pagoda-like crown silhouette on mature trees.
+          <t>Flowers: White to pale pink, appearing on bare branches in late winter before leaf flush. Open at night and close by midday. Pungent scent attracts bats and moths. Not ornamentally showy but an important ecological event.
+Fruit and Seeds: Ellipsoid woody capsules 3 to 6 inches long. Each contains up to 200 seeds embedded in silky kapok fiber. A single tree can produce up to 4,000 pods per season. Fiber is hollow, buoyant, and water-resistant.
+Leaves: Palmate compound, with 5 to 9 long narrow leaflets radiating from a central point. Deciduous — drops leaves during dry season, which is when flowering occurs.
+Trunk: Massive, buttressed at the base with wide spreading roots. Large conical spines on trunk and major branches. Horizontal branching creates a distinctive pagoda-like crown silhouette on mature trees.
 What to Look For: The spiny trunk is visible year-round and immediately distinguishes it from the adjacent Red Silk Cotton Trees, which share the same growth form. The horizontal branching pattern is the mature tree's signature. In late winter, watch for flowers on bare branches before the leaves return.</t>
         </is>
       </c>
@@ -11530,22 +11527,24 @@
       <c r="H62" s="32" t="n"/>
       <c r="I62" s="33" t="inlineStr">
         <is>
-          <t>The flower lasts only a single morning — each bloom opens at dawn and is gone by noon. The plant compensates by producing them in succession over a long season.
-After flowering, the stem tip bends to the ground, roots where it touches, and starts a new plant. This is the walk — slow, lateral, relentless.
-Member of the iris family. The whole Iridaceae family should be kept away from dogs — the rhizomes in particular contain compounds that cause digestive upset.
-Forms spreading clumps over time. Tolerates a surprising range of conditions including waterlogged soil and drought once established.</t>
+          <t>The flower lasts only a **single morning** — each bloom opens at dawn and is gone by noon. The plant compensates by producing them in succession over a long season.
+After flowering, the stem tip bends to the ground, roots where it touches, and starts a new plant. This is **the walk** — slow, lateral, relentless.
+Member of the iris family. The whole Iridaceae family should be **kept away from dogs** — the rhizomes in particular contain compounds that cause digestive upset.
+Forms **spreading clumps** over time. Tolerates a surprising range of conditions including waterlogged soil and drought once established.
+For years this plant was mislabeled **African iris** around the park — but the two are genuinely different. The real African iris grows by the pond on Welcome Island, a short walk away, if you'd like to compare them side by side.</t>
         </is>
       </c>
       <c r="J62" s="33" t="inlineStr">
         <is>
-          <t>Non-native. Native to southern Mexico, Central America, Colombia, and Venezuela. Member of Iridaceae — the iris family. Sometimes listed under the synonym Trimezia martinicensis.</t>
+          <t>Non-native. Native to southern Mexico, Central America, Colombia, and Venezuela. Member of Iridaceae — the iris family.</t>
         </is>
       </c>
       <c r="K62" s="33" t="inlineStr">
         <is>
-          <t>The yellow walking iris earns its name through a simple mechanism: after the flower stalk finishes blooming, the tip arches down to the ground. Wherever it makes contact, it roots and produces a new plant. The original clump extends itself laterally across a garden bed without any human assistance, one plantlet at a time.
+          <t>The yellow walking iris earns its name through a simple mechanism: after the flower stalk finishes blooming, the tip arches down to the ground. Wherever it makes contact, it roots and produces a new plant. One plantlet at a time, the clump travels laterally across a bed.
 The flowers themselves are short-lived by design. Each bloom opens in the morning and closes permanently by midday — a single morning per flower, with new ones following in succession. The effect across a clump in bloom is a daily rotation of fresh flowers.
-The iris family as a whole contains compounds — primarily in the rhizomes — that cause digestive irritation in dogs. While Trimezia is not specifically listed by ASPCA, the Iridaceae family listing is broad enough to warrant caution.</t>
+For a long stretch this plant was labeled African iris around the park, and the mix-up is understandable — both grow the same fan of sword-shaped leaves. But they are different plants. If you want to see for yourself, the park's African iris grows by the pond on Welcome Island, a short walk from here; side by side, the flowers and habit give them away.
+Like true irises, this plant carries irritant compounds — historically called irisin, concentrated in the rhizomes — that cause digestive upset in dogs and cats. ASPCA flags irises as toxic, and the walking iris shares the same chemistry, so it is worth keeping curious pets from digging at the roots.</t>
         </is>
       </c>
       <c r="L62" s="33" t="inlineStr">
@@ -11556,17 +11555,16 @@
       </c>
       <c r="M62" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Bright yellow with brown spots, iris-shaped, appearing on arching stems above the foliage. Each flower opens at dawn and closes by midday — one morning per bloom. New flowers follow in succession.
-Vegetative Spread — After flowering, the stem tip arches to the ground and roots on contact, producing a new plantlet. This is the walking mechanism. Clumps expand steadily outward over time.
-Leaves — Long, narrow, sword-shaped, in a fan arrangement typical of the iris family. Medium green.
-Form — Clumping, 2 to 4 feet tall. Spreads slowly but persistently by the walking stem-tip rooting.
+          <t>Flowers: Bright yellow with brown spots, iris-shaped, appearing on arching stems above the foliage. Each flower opens at dawn and closes by midday — one morning per bloom. New flowers follow in succession.
+Vegetative Spread: After flowering, the stem tip arches to the ground and roots on contact, producing a new plantlet. This is the walking mechanism. Clumps expand steadily outward over time.
+Leaves: Long, narrow, sword-shaped, in a fan arrangement typical of the iris family. Medium green.
+Form: Clumping, 2 to 4 feet tall. Spreads slowly but persistently by the walking stem-tip rooting.
 What to Look For: The iris-shaped yellow flowers with brown spots are distinctive. In the morning they are open; by noon they are closed. Look for arching stem tips touching the ground at the edge of established clumps — those are the next generation taking root.</t>
         </is>
       </c>
       <c r="N62" s="33" t="inlineStr">
         <is>
-          <t>Typically 2 to 3 feet tall (sometimes taller), forming spreading clumps. Plant habit: upright, grassy, clump-forming groundcover. Growth rate: moderate to fast, spreading over time. Texture: medium, fine sword-like foliage.</t>
+          <t>Typically 2 to 4 feet tall, forming spreading clumps. Plant habit: upright, grassy, clump-forming groundcover. Growth rate: moderate to fast, spreading over time. Texture: medium, fine sword-like foliage.</t>
         </is>
       </c>
       <c r="O62" s="33" t="inlineStr">
@@ -11601,7 +11599,7 @@
       </c>
       <c r="U62" s="31" t="inlineStr">
         <is>
-          <t>Caution. The iris family (Iridaceae) is listed by ASPCA as toxic to dogs — rhizomes contain the highest concentration. Ingestion may cause drooling, vomiting, and lethargy. Keep dogs from digging the rhizomes.</t>
+          <t>Caution. ASPCA lists irises as toxic to dogs and cats, and the walking iris shares the same irritant compounds — most concentrated in the rhizomes. Ingestion may cause drooling, vomiting, and lethargy. Keep dogs from digging up the roots.</t>
         </is>
       </c>
       <c r="V62" s="36" t="inlineStr">
@@ -11680,10 +11678,10 @@
       </c>
       <c r="I63" s="33" t="inlineStr">
         <is>
-          <t>The standard ixora is red — Jungle Flame is its most common nickname. The Maui Yellow cultivar trades that for a soft golden-yellow that reads differently in the landscape: warmer, less assertive, more quietly tropical.
-Ixora is one of the more thoroughly studied butterfly nectar plants for Florida gardens. The tubular flower clusters are accessible to butterflies and hummingbirds but not to most insects with shorter mouthparts.
-Sensitive to cold and to high-pH soil — alkaline conditions cause chlorosis, a yellowing of the leaves that is a common problem in Florida where soils tend toward alkaline. Acid fertilizer or soil amendment fixes it.
-Native to India and Sri Lanka. In its home range a significant plant in Buddhist and Hindu temple culture.</t>
+          <t>The standard ixora is red — Jungle Flame is a common nickname. The Maui Yellow cultivar trades that for a soft **golden-yellow** that reads differently in the landscape: warmer, less assertive, more quietly tropical.
+Ixora is one of the more reliable butterfly nectar plants for Florida gardens. The tubular flower clusters are accessible to **butterflies and hummingbirds** but not to most insects with shorter mouthparts.
+Sensitive to cold and to high-pH soil — alkaline conditions cause **chlorosis**, a yellowing of the leaves that is a common problem in Florida where soils tend toward alkaline. Acid fertilizer or soil amendment fixes it.
+Native to India and Sri Lanka. In its home range a significant plant in Buddhist and Hindu **temple culture**.</t>
         </is>
       </c>
       <c r="J63" s="33" t="inlineStr">
@@ -11693,7 +11691,7 @@
       </c>
       <c r="K63" s="33" t="inlineStr">
         <is>
-          <t>The standard-issue ixora in Florida landscapes is the red-bracted Jungle Flame — a reliable and widely used flowering shrub that can blur into the background through familiarity. The Maui Yellow cultivar steps back from that intensity with soft golden-yellow flower clusters that hold their color over a long bloom season.
+          <t>The standard-issue ixora in Florida landscapes is the red-flowered Jungle Flame — a reliable and widely used flowering shrub that can blur into the background through familiarity. The Maui Yellow cultivar steps back from that intensity with soft golden-yellow flower clusters that hold their color over a long bloom season.
 Ixora is sensitive to soil pH in a way that shows quickly. Alkaline soils cause interveinal chlorosis — the leaves yellow while the veins stay green, giving the plant a faded, stressed appearance. In Florida where soils often trend alkaline, this is a common issue with ixora. Acid fertilizer or soil acidification corrects it promptly. A plant that looks unhealthy here is often just in the wrong soil chemistry, not actually ill.
 In its native India and Sri Lanka, ixora has deep roots in temple culture — the flowers are used in Hindu and Buddhist religious offerings, garlands, and ceremonies. The genus name Ixora derives from a Portuguese rendering of Isvara, a Sanskrit name for the Hindu deity Shiva.</t>
         </is>
@@ -11706,11 +11704,10 @@
       </c>
       <c r="M63" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Dense, rounded clusters (cymes) of tubular four-petaled flowers in golden yellow (this cultivar). Blooms throughout warm months with peak flowering spring through fall.
-Fruit — Small, dark, berry-like drupes. Rarely significant ornamentally.
-Leaves — Opposite, glossy, dark green, oval to oblong. New growth often has a reddish-bronze tint. Yellowing with green veins (interveinal chlorosis) indicates alkaline soil conditions — respond with acid fertilizer or soil amendment.
-Form — Evergreen shrub, typically 4 to 6 feet tall and wide; can reach 8 to 10 feet unpruned. Dense branching.
+          <t>Flowers: Dense, rounded clusters (cymes) of tubular four-petaled flowers in golden yellow (this cultivar). Blooms throughout warm months with peak flowering spring through fall.
+Fruit: Small, dark, berry-like drupes. Rarely significant ornamentally.
+Leaves: Opposite, glossy, dark green, oval to oblong. New growth often has a reddish-bronze tint. Yellowing with green veins (interveinal chlorosis) indicates alkaline soil conditions — respond with acid fertilizer or soil amendment.
+Form: Evergreen shrub, typically 4 to 6 feet tall and wide; can reach 8 to 10 feet unpruned. Dense branching.
 What to Look For: The golden-yellow flower clusters against dark glossy leaves. Distinguish from standard red ixora by flower color. Yellowing leaves with green veins are a soil chemistry signal, not disease.</t>
         </is>
       </c>
@@ -11786,6 +11783,11 @@
           <t>Standard</t>
         </is>
       </c>
+      <c r="AD63" s="45" t="inlineStr">
+        <is>
+          <t>CULTIVAR POLICY (Randy 2026-06-11): handle cultivars via the SPECIES card, listing the cultivars the park has; hero photo/content representative, not cultivar-exact. Do NOT append cultivar epithets to sci-name. This card may later be folded into a species-level Ixora coccinea card.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="255.65" customHeight="1" s="58">
       <c r="A64" s="29" t="inlineStr">
@@ -11826,49 +11828,55 @@
       <c r="H64" s="32" t="n"/>
       <c r="I64" s="33" t="inlineStr">
         <is>
-          <t>Not bamboo. Not even distantly related to bamboo. The resemblance is in the cane-like stems and compound leaves — the botany is completely different.
-FISC Category I invasive in Florida — the highest listing. Spreads into natural areas via bird-dispersed seeds. Birds eat the berries readily, which is part of the problem.
-The berries contain cyanogenic compounds. Cedar Waxwings have been documented dying of cyanide poisoning after gorging on Nandina berries in Georgia. Small quantities are generally tolerated; large quantities are not.
-This specimen is kept as an educational example — a demonstration of why a plant can be beautiful, popular, and ecologically harmful simultaneously.</t>
+          <t>**Not bamboo**. Not even distantly related to bamboo. The resemblance is in the cane-like stems and compound leaves — the botany is completely different.
+**FISC Category I** invasive in Florida — the highest listing. Spreads into natural areas via bird-dispersed seeds. Birds eat the berries readily, which is part of the problem.
+The berries contain **cyanogenic glycosides** — generally tolerated in small amounts, but capable of killing voracious feeders like Cedar Waxwings that gorge on them.
+This specimen is kept as an **educational example** — a demonstration of why a plant can be beautiful, popular, and ecologically harmful simultaneously.</t>
         </is>
       </c>
       <c r="J64" s="33" t="inlineStr">
         <is>
-          <t>Non-native. Native to eastern Asia from the Himalayas through China to Japan. Member of Berberidaceae — the barberry family. Introduced to the United States in 1804 as an ornamental.</t>
+          <t>Non-native. Native to eastern Asia from the Himalayas through China to Japan. Member of Berberidaceae — the barberry family. Introduced to the United States in the early 1800s as an ornamental.</t>
         </is>
       </c>
       <c r="K64" s="33" t="inlineStr">
         <is>
           <t>Heavenly Bamboo is a Category I invasive in Florida — the highest FISC designation — yet it remains widely sold and planted in Florida landscapes. The combination of attractive appearance, easy care, and bird-dispersed red berries has made it a persistent presence in nurseries even as its ecological damage is well documented. It spreads into woodlands and floodplains and displaces native vegetation.
-The berry toxicity story is specific and documented. In 2010, veterinary pathologists in Georgia performed necropsies on dozens of Cedar Waxwings that had died after eating Nandina berries. The birds showed tissue hemorrhaging consistent with cyanide poisoning. The leaves and unripe green berries are highly cyanogenic; ripe red berries release cyanide more slowly and become less toxic as they age on the plant. Most birds consuming small quantities are unaffected, but Cedar Waxwings are voracious feeders that can consume large quantities quickly, pushing past the safe threshold.
-Two cultivars — Harbour Dwarf and Firepower — are considered safe options by UF/IFAS assessment. The standard species is not recommended for planting in Florida.
+One question visitors often ask is what the species name domestica means. It points to household — fitting for a plant with a long domestic history across China and Japan, where it was traditionally planted beside the front door as a sacred protector, believed to ward off misfortune and dissipate bad dreams. There is a quiet irony in that: a plant once set out to guard the home is, in the southeastern United States, one of the more destructive escapees from cultivation.
+The berry toxicity story is specific and documented. Veterinary pathologists in Georgia documented dozens of Cedar Waxwings that died after gorging on Nandina berries, with tissue hemorrhaging consistent with cyanide poisoning. The leaves and unripe green berries are highly cyanogenic; ripe red berries release cyanide more slowly and become less toxic as they age on the plant. Most birds consuming small quantities are unaffected, but Cedar Waxwings are voracious feeders that can consume large quantities quickly, pushing past the safe threshold.
+Two cultivars — Harbour Dwarf and Firepower — are considered lower-risk alternatives by UF/IFAS assessment (they rarely fruit, limiting spread). The standard species is not recommended for planting in Florida.
 This plant is kept here as an educational specimen in the Invasive Awareness context.</t>
         </is>
       </c>
       <c r="L64" s="33" t="inlineStr">
         <is>
-          <t>The berries attract birds, which then disperse seeds into natural areas — this is the primary mechanism of its spread and the core ecological harm. The plant provides food, but the food vehicle carries seeds that establish invasive populations away from cultivation.
-Cedar Waxwings and other frugivorous birds visit readily. The risk is not in a bird eating a few berries — it is in the cumulative seed dispersal into natural areas, and in flocks of voracious feeders consuming toxic quantities.</t>
+          <t>Nandina poses a paradox of wildlife value: its bright berries are readily eaten by Cedar Waxwings and other frugivorous birds, but that very service is the harm. The risk is not a single bird taking a few berries — it is the cumulative dispersal of seed into native woodlands and floodplains, where new invasive populations establish far from any garden. A food source that ultimately works against the ecosystem feeding on it.</t>
         </is>
       </c>
       <c r="M64" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Small, white, in upright clusters in spring. Not ornamentally significant.
-Fruit — Bright red berries in clusters, persisting into winter. Highly attractive to birds. Contains cyanogenic compounds — toxic in quantity, particularly to species that feed rapidly in large amounts.
-Leaves — Compound, with small pointed leaflets that turn red-orange in cool weather. New growth often reddish. Bamboo-like cane stems with multi-leafed, fern-like compound foliage.
-Form — Upright evergreen shrub, 4 to 8 feet tall, with slender cane-like stems.
+          <t>Flowers: Small, white, in upright clusters in spring. Not ornamentally significant.
+Fruit: Bright red berries in clusters, persisting into winter. Highly attractive to birds. Contains cyanogenic compounds — toxic in quantity, particularly to species that feed rapidly in large amounts.
+Leaves: Compound, with small pointed leaflets that turn red-orange in cool weather. New growth often reddish. Bamboo-like cane stems with multi-leafed, fern-like compound foliage.
+Form: Upright evergreen shrub, 4 to 8 feet tall, with slender cane-like stems.
 What to Look For: The compound foliage on bamboo-like stems and the red berry clusters in fall and winter. Compare to true bamboo: Nandina has compound leaves (many leaflets on one stem), true bamboo has simple leaves.</t>
         </is>
       </c>
       <c r="N64" s="33" t="inlineStr">
         <is>
-          <t>An upright evergreen shrub, typically 4 to 8 feet tall, with slender, cane-like, lightly branched stems that give it a bamboo-like silhouette. The fine-textured, lacy compound leaves often flush red or scarlet in cold weather.</t>
+          <t>Height/Length: 4 to 8 feet
+Habit: upright evergreen shrub; slender, cane-like, lightly branched stems (bamboo-like silhouette)
+Texture: fine, lacy compound foliage</t>
         </is>
       </c>
       <c r="O64" s="33" t="inlineStr">
         <is>
-          <t>Tough and highly adaptable — tolerates drought, deep shade, salt, and a wide range of soils, and is largely free of pests and deer browsing. USDA zones 6 to 9. That very toughness is what allows it to escape gardens and establish in natural areas.</t>
+          <t>Light: full sun to deep shade (very adaptable)
+Soil: wide range; highly adaptable
+Drought tolerance: high
+Salt tolerance: tolerant
+Cold tolerance: USDA zones 6 to 9
+Note: largely free of pests and deer browsing; that toughness is what lets it escape into natural areas</t>
         </is>
       </c>
       <c r="P64" s="34" t="inlineStr">
@@ -11898,7 +11906,7 @@
       </c>
       <c r="U64" s="31" t="inlineStr">
         <is>
-          <t>Toxic to dogs and cats. Berries contain cyanogenic compounds; ingestion causes hemorrhage and can be fatal. Cedar Waxwings have died from eating Nandina berries in documented cases. Keep pets away.</t>
+          <t>Toxic to dogs and cats. All parts contain cyanogenic glycosides; ingestion can cause hemorrhaging and may be fatal. Keep pets away, and contact a veterinarian or Poison Control if ingestion is suspected.</t>
         </is>
       </c>
       <c r="V64" s="36" t="inlineStr">
@@ -11923,10 +11931,15 @@
       </c>
       <c r="Z64" s="33" t="inlineStr">
         <is>
-          <t>Also known as sacred bamboo or nanten. Not a true bamboo despite the common name — it is a member of the barberry family.</t>
-        </is>
-      </c>
-      <c r="AA64" s="33" t="n"/>
+          <t>Sacred Bamboo
+Nanten</t>
+        </is>
+      </c>
+      <c r="AA64" s="33" t="inlineStr">
+        <is>
+          <t>This one is tucked into a small, easy-to-miss spot on Welcome Island, largely crowded out by the Tree Crinum mass planting around it — and it usually looks a little unkempt thanks to its different coloring. Whether it is the Tree Crinums holding it back or simply the nature of a single contained specimen, we have seen zero evidence of spread here. That fits the larger picture: Nandina's documented harm comes from birds carrying its seed into natural areas, not from one hemmed-in garden plant — which is exactly why it stays here as a teaching example rather than a recommendation.</t>
+        </is>
+      </c>
       <c r="AB64" s="33" t="inlineStr">
         <is>
           <t>Flowering Shrubs and Vines</t>
@@ -11935,6 +11948,11 @@
       <c r="AC64" s="31" t="inlineStr">
         <is>
           <t>Standard</t>
+        </is>
+      </c>
+      <c r="AD64" s="45" t="inlineStr">
+        <is>
+          <t>Single contained specimen, Welcome Island, crowded by Tree Crinum mass planting; no spread observed here (Randy field obs 2026-06-11). FISC Cat I confirmed.</t>
         </is>
       </c>
     </row>
@@ -11977,10 +11995,10 @@
       <c r="H65" s="32" t="n"/>
       <c r="I65" s="33" t="inlineStr">
         <is>
-          <t>The genus name Sagittaria comes from the Latin for arrow — named for the unmistakable arrowhead shape of the leaves. The shape is so distinctive that it has been the identifying feature of this plant since before botanical Latin was invented.
-The starchy underground tubers — duck potatoes — were a staple food for Indigenous peoples across the southeastern United States and were gathered and traded widely. Ducks and muskrats eat them too, which is where the folk name comes from.
-An emergent aquatic native — grows with its roots in the water and its foliage above the surface. Stabilizes shallow pond banks by rhizome.
-The flowers are three-petaled and white with a yellow center — simple, clean, and worth a look up close.</t>
+          <t>The genus Sagittaria takes its name from the Latin for arrow — most of its members have arrowhead-shaped leaves. This one is the exception: its leaves are narrow and **lance-shaped**, which is just what ‘lancifolia’ means.
+The starchy underground tubers — **duck potatoes** — were a staple food for Indigenous peoples across the southeastern United States and were gathered and traded widely. Ducks and muskrats eat them too, which is where the folk name comes from.
+An **emergent aquatic** native — grows with its roots in the water and its foliage above the surface. Stabilizes shallow pond banks by rhizome.
+The flowers are **three-petaled** and white with a yellow center — simple, clean, and worth a look up close.</t>
         </is>
       </c>
       <c r="J65" s="33" t="inlineStr">
@@ -11992,7 +12010,7 @@
         <is>
           <t>Lanceleaf Arrowhead is one of the more historically significant plants at the water's edge. The tubers — called duck potatoes — were a reliable starchy food source for Indigenous peoples across the Southeast, harvested by wading into shallow water and loosening them from the mud with their feet or toes. The tubers float to the surface once freed. They were eaten roasted or boiled and were traded between communities. European settlers adopted the same practice.
 The plant is doing active ecological work in the ponds. The rhizome network stabilizes the shallow bank zone, and the emergent foliage creates habitat structure at the water surface used by fish, frogs, aquatic insects, and wading birds. Ducks and muskrats eat the tubers; blackbirds and other waterbirds eat the seeds.
-The arrowhead leaf shape is one of the more distinctive silhouettes in the Florida wetland plant palette — recognizable at a distance, unambiguous up close.</t>
+Its leaves are the giveaway to its name. The genus Sagittaria is named for the bold arrowhead foliage of most of its members, but this one — lancifolia, literally ‘lance-leaved’ — is the exception, carrying smooth, narrow, tapering blades rather than deep arrowhead lobes. The common name Lanceleaf Arrowhead captures exactly that contradiction.</t>
         </is>
       </c>
       <c r="L65" s="33" t="inlineStr">
@@ -12003,23 +12021,28 @@
       </c>
       <c r="M65" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Three white petals with a yellow center, on branched stalks rising above the foliage. Male and female flowers sometimes on separate stalks on the same plant. Clean and simple up close.
-Fruit and Seeds — Rounded heads of small flattened seeds eaten by waterbirds.
-Tubers — Starchy underground tubers (duck potatoes) along the rhizomes. Edible — historically roasted or boiled. Eaten by ducks, muskrats, and other wetland wildlife.
-Leaves — Strongly arrowhead-shaped (sagittate), on long petioles rising from the water. Very variable in size. The shape is the definitive identification feature.
-Form — Emergent aquatic perennial, 2 to 5 feet above water. Spreads by rhizomes to form colonies in shallow water and saturated soil.
-What to Look For: The arrowhead leaf shape is unmistakable — no other plant at the pond edge has quite that silhouette. White three-petaled flowers on tall stalks above the foliage when in bloom.</t>
+          <t>Flowers: Three white petals with a yellow center, on branched stalks rising above the foliage. Male and female flowers sometimes on separate stalks on the same plant. Clean and simple up close.
+Fruit and Seeds: Rounded heads of small flattened seeds eaten by waterbirds.
+Tubers: Starchy underground tubers (duck potatoes) along the rhizomes. Edible — historically roasted or boiled. Eaten by ducks, muskrats, and other wetland wildlife.
+Leaves: Lance-shaped (lanceolate) to elliptic, smooth, on long petioles rising from the water — to about 10 inches long, and variable in size. Unlike most arrowheads, the blades lack the deep arrowhead lobes; that narrow lance shape is the key ID feature for this species.
+Form: Emergent aquatic perennial, 2 to 5 feet above water. Spreads by rhizomes to form colonies in shallow water and saturated soil.
+What to Look For: Narrow, lance-shaped leaves on long petioles — not the deep arrowhead lobes the genus name suggests. The white three-petaled flowers on tall stalks above the foliage are the clincher when in bloom.</t>
         </is>
       </c>
       <c r="N65" s="33" t="inlineStr">
         <is>
-          <t>An emergent aquatic perennial, typically 3 to 5 feet tall (occasionally taller), forming clumps 1 to 3 feet wide. The smooth, lance-shaped leaf blades can reach about 10 inches long.</t>
+          <t>Height/Length: 2 to 5 feet (occasionally taller)
+Spread: clumps 1 to 3 feet wide
+Habit: emergent aquatic perennial, clump-forming</t>
         </is>
       </c>
       <c r="O65" s="33" t="inlineStr">
         <is>
-          <t>Wants full sun and shallow standing water or consistently saturated soil — it grows along pond and lake edges, in freshwater and brackish marshes, and at muddy stream margins. It should not be allowed to dry out, and it has little tolerance for direct salt spray. A classic choice for water gardens, rain gardens, and wetland restoration.</t>
+          <t>Light: full sun
+Water: shallow standing water or consistently saturated soil; do not let it dry out
+Soil: pond and lake edges, freshwater and brackish marshes, muddy stream margins
+Salt tolerance: low; little tolerance for direct salt spray
+Uses: water gardens, rain gardens, wetland restoration</t>
         </is>
       </c>
       <c r="P65" s="34" t="inlineStr">
@@ -12074,10 +12097,15 @@
       </c>
       <c r="Z65" s="33" t="inlineStr">
         <is>
-          <t>Also called bulltongue arrowhead and duck potato. Sometimes treated as subspecies or varieties (for example subsp. media). Carries many historical scientific synonyms, including Sagittaria angustifolia and Sagittaria ovata.</t>
-        </is>
-      </c>
-      <c r="AA65" s="33" t="n"/>
+          <t>Bulltongue Arrowhead
+Duck Potato</t>
+        </is>
+      </c>
+      <c r="AA65" s="33" t="inlineStr">
+        <is>
+          <t>For years, volunteers tried establishing duck potato — and pickerelweed alongside it — in the park's ponds with little success, even though both are standard recommendations for Florida ponds. The reason surfaced during the pond restoration project: measurements showed our ponds run saltier than most inland ponds, since they connect to the bay by pipe. This specimen survives because of where it sits — the pond farthest from the bay and nearest the point where fresh water arrives from the county water tank just off the park boundary. That corner stays just fresh enough, often enough, that this stubborn native keeps coming back.</t>
+        </is>
+      </c>
       <c r="AB65" s="33" t="inlineStr">
         <is>
           <t>Native Wetland and Pond Edge</t>
@@ -12086,6 +12114,11 @@
       <c r="AC65" s="31" t="inlineStr">
         <is>
           <t>Standard</t>
+        </is>
+      </c>
+      <c r="AD65" s="45" t="inlineStr">
+        <is>
+          <t>Field history: KML split-duplicate (categorized pin + Unobserved 'TOUGH TO GROW') — merge per May-2026 reconciliation. Park ponds higher salinity (bay-connected by pipe); duck potato &amp; pickerelweed repeatedly failed except in freshest pond nearest county water-tank inflow, where this specimen persists. Randy field obs 2026-06-11.</t>
         </is>
       </c>
     </row>
@@ -12155,12 +12188,11 @@
       </c>
       <c r="M66" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Figs — Small, round, green ripening to yellow-orange to red, produced year-round in multiple crops. Eaten by a wide range of wildlife. Each fig is technically a syconium — a hollow structure lined with flowers, pollinated by a specific fig wasp that enters and dies inside.
-Leaves — Oval to oblong, leathery, dark glossy green. Evergreen. Smooth margin.
-Aerial Roots — Long, rope-like roots descending from branches and trunk, characteristic of the species. On mature trees these fuse together forming a distinctive lattice structure around what was once the host trunk.
-Milky Latex — White sap from cut stems or leaves. Mild skin irritant; avoid contact with eyes.
-Form — Large evergreen tree to 50 to 100 feet. Broad spreading canopy. Often hollow at the center on old specimens.
+          <t>Figs: Small, round, green ripening to yellow-orange to red, produced year-round in multiple crops. Eaten by a wide range of wildlife. Each fig is technically a syconium — a hollow structure lined with flowers, pollinated by a specific fig wasp that enters and dies inside.
+Leaves: Oval to oblong, leathery, dark glossy green. Evergreen. Smooth margin.
+Aerial Roots: Long, rope-like roots descending from branches and trunk, characteristic of the species. On mature trees these fuse together forming a distinctive lattice structure around what was once the host trunk.
+Milky Latex: White sap from cut stems or leaves. Mild skin irritant; avoid contact with eyes.
+Form: Large evergreen tree to 50 to 100 feet. Broad spreading canopy. Often hollow at the center on old specimens.
 What to Look For: The aerial roots descending from branches are the year-round identification feature. The small figs in various stages of ripening throughout the year. The hollow center on very old trees.</t>
         </is>
       </c>
@@ -12280,10 +12312,10 @@
       <c r="H67" s="32" t="n"/>
       <c r="I67" s="33" t="inlineStr">
         <is>
-          <t>One of Florida's three classic scrub oaks, and the smallest. In scrub habitat it regenerates from underground stems after fire — the above-ground plant burns, the root system survives, and new shoots emerge within weeks.
-The small, leathery, oval leaves with rolled-under margins are an adaptation to dry, exposed conditions — reducing water loss on the driest, sandiest soils in Florida.
-The acorns, produced abundantly, are a critical food source for Florida Scrub-Jays — a species that caches acorns as its primary winter food strategy and is entirely dependent on scrub oak habitat for survival.
-Here at the park it is not in scrub. It is growing outside its typical habitat, which is worth noting.</t>
+          <t>One of Florida's three classic **scrub oaks**, and the one with the smallest leaves. In scrub habitat it regenerates from underground stems after fire — the above-ground plant burns, the root system survives, and new shoots emerge within weeks.
+The small, leathery, oval leaves with **rolled-under margins** are an adaptation to dry, exposed conditions — reducing water loss on the driest, sandiest soils in Florida.
+The abundant acorns are a crucial food source for **Florida Scrub-Jays**.
+Here at the park it grows **outside its native scrub** — a chance to see how a fire-adapted scrub oak takes shape in the gentler, more sheltered conditions of a garden than in the harsh white sand it evolved for.</t>
         </is>
       </c>
       <c r="J67" s="33" t="inlineStr">
@@ -12294,6 +12326,8 @@
       <c r="K67" s="33" t="inlineStr">
         <is>
           <t>Myrtle Oak is a scrub specialist, meaning it evolved specifically for one of Florida's most extreme habitats: ancient, nutrient-poor, white sand scrub where most plants cannot survive and fire is the defining ecological process. In this habitat, the Myrtle Oak does not grow as a tree — it grows as a dense, sprawling shrub, often just a few feet tall, regenerating repeatedly from a deep root system that survives fire when the above-ground portions burn.
+This is why the same species can look so different from one place to the next. In regularly burned scrub, fire keeps it a stunted, multi-stemmed shrub. Spared from fire — as it is here at the park — that very same oak can stretch into a single-trunked small tree of thirty feet or more. The difference in form comes down almost entirely to how often it burns: a living lesson in how environment, not just genetics, sculpts a plant.
+Those slightly in-rolled (revolute) leaf margins are more than an ID trait — they are working machinery. By curling under, the edges help trap a thin layer of still, humid air against the leaf's underside, where the breathing pores (stomata) sit. That sheltered pocket buffers them from hot, drying winds and trims the plant's water loss — a small structural trick with real value on Florida's driest sands.
 The relationship with the Florida Scrub-Jay is one of the more well-documented plant-animal dependencies in Florida conservation. The Scrub-Jay caches acorns as its primary winter food source, burying them individually in the sand. Myrtle Oak acorns are among the most important in its diet. Without adequate acorn production from scrub oaks, Scrub-Jay populations decline. The reverse is also documented — Scrub-Jay caching behavior contributes to oak recruitment by burying seeds at the right depth and in suitable locations.
 Florida scrub is one of the most threatened habitats in the state, with an estimated 90% having been lost to development. The Scrub-Jay is listed as threatened. The Myrtle Oak, by contrast, is secure — but its security depends on the survival of the habitat.</t>
         </is>
@@ -12306,22 +12340,28 @@
       </c>
       <c r="M67" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Acorns — Small, rounded, produced in good quantities. Mature in two years (red oak group). Critical food source for Florida Scrub-Jays and other wildlife.
-Leaves — Small, oval to oblong, leathery, with margins that roll under slightly (revolute). Dark glossy green above, paler below. Evergreen. This rolled margin is a key ID feature distinguishing it from other small oaks.
-Form — Evergreen shrub to small tree, usually 5 to 20 feet in typical scrub conditions; can grow taller in protected settings. Multi-stemmed, dense, spreading.
-Bark — Gray-brown, furrowed on older stems.
-What to Look For: The small, leathery oval leaves with the characteristic rolled-under margins are the best year-round ID feature. Compare with the other oaks at the park — the leaf scale and texture are distinctive.</t>
+          <t>Acorns: Small, rounded, produced in good quantities. Mature in two years (red oak group). Critical food source for Florida Scrub-Jays and other wildlife.
+Leaves: Small (about ¾ inch to 2 inches long), oval to oblong, leathery, with margins that roll under slightly (revolute). Dark glossy green above, paler below. Evergreen. This rolled margin is a key ID feature distinguishing it from other small oaks.
+Form: Evergreen shrub to small tree, usually 5 to 20 feet in typical scrub conditions; can grow taller in protected settings. Multi-stemmed, dense, spreading.
+Bark: Gray-brown, furrowed on older stems.
+What to Look For: The small, leathery oval leaves with the characteristic rolled-under margins are the best year-round ID feature. Compare with the other oaks at the park — the leaf scale and texture are distinctive. It can be confused with the closely related Florida scrub oak (Quercus inopina) and Chapman's oak (Quercus chapmanii); the small, rolled-under leaves help separate it.</t>
         </is>
       </c>
       <c r="N67" s="33" t="inlineStr">
         <is>
-          <t>An evergreen shrub to small tree, usually 5 to 20 feet tall (occasionally reaching 35 to 40 feet), often densely branched and shrubby. The leaves are small — roughly three-quarters of an inch to 2 inches long — thick, leathery, and shiny dark green above.</t>
+          <t>Height/Length: 5 to 20 feet (occasionally 35 to 40 feet)
+Habit: evergreen shrub to small tree, densely branched and shrubby</t>
         </is>
       </c>
       <c r="O67" s="33" t="inlineStr">
         <is>
-          <t>A tough native of dry, sunny, sandy sites. It prefers full sun to part shade and well-drained, acidic, sandy soil; it is highly drought-tolerant and needs no supplemental water once established. Good hurricane-wind resistance and moderate salt tolerance make it well suited to coastal plantings. USDA zones 8 to 10. Fire-adapted.</t>
+          <t>Light: full sun to part shade
+Soil: well-drained, acidic, sandy
+Drought tolerance: high; no supplemental water once established
+Salt tolerance: moderate
+Wind: good hurricane-wind resistance
+Cold tolerance: USDA zones 8 to 10
+Note: fire-adapted; well suited to coastal plantings</t>
         </is>
       </c>
       <c r="P67" s="34" t="inlineStr">
@@ -12374,11 +12414,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z67" s="33" t="inlineStr">
-        <is>
-          <t>One of Florida's three classic scrub oaks. Belongs to the red oak group. Can be confused with the closely related Florida scrub oak (Quercus inopina) and Chapman's oak (Quercus chapmanii).</t>
-        </is>
-      </c>
+      <c r="Z67" s="33" t="n"/>
       <c r="AA67" s="33" t="n"/>
       <c r="AB67" s="33" t="inlineStr">
         <is>
@@ -12430,10 +12466,11 @@
       <c r="H68" s="32" t="n"/>
       <c r="I68" s="33" t="inlineStr">
         <is>
-          <t>The real attraction is not the flower but what follows it — a large, waxy, inflated calyx in deep red-purple that persists and swells as the fruit develops inside. The calyx is the show.
-The flowers themselves are a fleeting display: long white tubes with dramatically extended purple stamens, 3 to 5 inches long. They drop quickly, setting the stage for the calyx.
-Native to tropical Asia. Member of Lamiaceae — the mint family — despite looking nothing like mint.
-The hollow stems were used historically across Asia as pipe stems, pen shafts, and blowgun tubes — the origin of its common name: tube flower.</t>
+          <t>The real attraction is not the flower but what follows it — a large, waxy, **inflated calyx** in deep red-purple that persists and swells as the fruit develops inside. The calyx is the show.
+The flowers themselves are a fleeting display: long white tubes with dramatically extended **purple stamens**, 3 to 5 inches long. They drop quickly, setting the stage for the calyx.
+Native to tropical Asia. Member of Lamiaceae — the **mint family** — despite looking nothing like mint.
+The hollow stems were used historically across Asia as pipe stems, pen shafts, and blowgun tubes — the origin of its common name: **tube flower**.
+At Palma Sola this is the **worst invasive in the park** — it suckers relentlessly from the roots, and we are constantly working to keep it in bounds.</t>
         </is>
       </c>
       <c r="J68" s="33" t="inlineStr">
@@ -12445,8 +12482,7 @@
         <is>
           <t>The Turk's Turban is a plant where the identifying feature is not the flower but what happens after it. The flowers are actually striking up close — long white tubes with dramatically extended purple stamens, 3 to 5 inches in length — but they are short-lived, dropping quickly to make way for the main event.
 What follows is the calyx: the leafy structure that surrounded the bud inflates after the petals fall into a large, waxy, ribbed, deep red-purple structure resembling a miniature lantern or a wrapped turban. Inside it, a small glossy black berry develops — the contrast of jet-black fruit against the red calyx is striking in its own right.
-The hollow stems have a long history of practical use across Southeast Asia — cut to length as pipe stems, pen shafts, and blowgun tubes. The common name tube flower references this directly. The plant spreads by suckering from its roots and forms colonies over time, which requires some management to keep it where it is wanted.
-In early June the white flower tubes are fully open at Palma Sola — long, elegant, with purple stamens extending well beyond the petals. They will not last long. What follows — the inflated red calyx cradling a glossy black berry — is already forming on stems where the flowers have dropped. If you are visiting now, you are catching the transition between two of the plant's best moments.</t>
+The hollow stems have a long history of practical use across Southeast Asia — cut to length as pipe stems, pen shafts, and blowgun tubes. The common name tube flower references this directly. The plant spreads aggressively by suckering from its roots, throwing up offsets well beyond the original clump — it needs active, ongoing management.</t>
         </is>
       </c>
       <c r="L68" s="33" t="inlineStr">
@@ -12457,23 +12493,28 @@
       </c>
       <c r="M68" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Small, tubular, white to pale lavender, at stem tips. Not ornamentally showy.
-Calyx — The defining feature. After petals fall, the calyx inflates into a large, waxy, ribbed, deep red-purple structure enclosing the developing fruit. Persistent and conspicuous. This is what most people notice.
-Fruit — Small, black, enclosed inside the inflated calyx.
-Leaves — Whorled, 3 to 5 leaves per node, broadly oval, medium green, with toothed margins. Occasionally opposite on young growth. Stems square in cross-section — the mint family signature.
-Form — Erect perennial shrub or subshrub, 3 to 6 feet tall, with hollow lightly branched stems. Spreads by root suckers.
-What to Look For: The large, waxy, red-purple inflated calyx structures are unlike anything else in the park — look for them at stem tips after flowering. Square stems confirm the mint family identification.</t>
+          <t>Flowers: Small, tubular, white to pale lavender, at stem tips. Not ornamentally showy.
+Calyx: The defining feature. After petals fall, the calyx inflates into a large, waxy, ribbed, deep red-purple structure enclosing the developing fruit. Persistent and conspicuous. This is what most people notice.
+Fruit: Small, black, enclosed inside the inflated calyx.
+Leaves: Whorled, 3 to 5 leaves per node, broadly oval, medium green, with toothed margins. Occasionally opposite on young growth. Stems square in cross-section — the mint family signature.
+Form: Erect perennial shrub or subshrub, 4 to 6 feet tall, with hollow lightly branched stems. Spreads aggressively by root suckers.
+What to Look For: The large, waxy, red-purple inflated calyx structures are unusual and hard to mistake — look for them at stem tips after flowering. Square stems confirm the mint family identification.</t>
         </is>
       </c>
       <c r="N68" s="33" t="inlineStr">
         <is>
-          <t>An erect perennial shrub or subshrub. The hollow, lightly branched stems commonly reach 4 to 6 feet and can stretch to 10 or even 12 feet in ideal conditions before flowering. The leaves are arranged in whorls around the stem.</t>
+          <t>Height/Length: 4 to 6 feet (to 10 or 12 feet in ideal conditions)
+Habit: erect perennial shrub or subshrub; hollow, lightly branched stems</t>
         </is>
       </c>
       <c r="O68" s="33" t="inlineStr">
         <is>
-          <t>Easy and adaptable in warm climates. It takes full sun to partial shade and a wide range of soils, preferring moist but well-drained ground, and is fairly drought-tolerant once established, though it has low tolerance for salt. Best in USDA zones 9 to 11; in cooler areas it is grown under glass or as a container plant. Its suckering habit means it can spread farther than you intend.</t>
+          <t>Light: full sun to partial shade
+Soil: wide range; prefers moist but well-drained
+Drought tolerance: fairly drought-tolerant once established
+Salt tolerance: low
+Cold tolerance: USDA zones 9 to 11 (under glass or container in cooler areas)
+Note: suckering habit spreads farther than intended; needs active management</t>
         </is>
       </c>
       <c r="P68" s="34" t="inlineStr">
@@ -12513,12 +12554,12 @@
       </c>
       <c r="W68" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="X68" s="30" t="inlineStr">
         <is>
-          <t>Not on Florida's FISC invasive plant list. Self-seeds and spreads by suckering — manage to prevent escape into adjoining natural areas.</t>
+          <t>Not on Florida's FISC invasive plant list, but reclassified to the park's Watch List based on field observation: it spreads aggressively by root suckers, throwing up offsets well beyond the original planting. Manage actively to prevent escape into adjoining beds and natural areas.</t>
         </is>
       </c>
       <c r="Y68" s="36" t="inlineStr">
@@ -12528,12 +12569,14 @@
       </c>
       <c r="Z68" s="33" t="inlineStr">
         <is>
-          <t>Also called tube flower, tubeflower, cathedral bells, and skyrocket. Originally described under the basionym Siphonanthus indicus and formerly placed in the family Verbenaceae; once carried the synonym Clerodendrum siphonanthus. Can be confused with other white-flowered Clerodendrum species.</t>
+          <t>Tube Flower
+Cathedral Bells
+Skyrocket</t>
         </is>
       </c>
       <c r="AA68" s="33" t="inlineStr">
         <is>
-          <t>NOMENCLATURE: Clerodendrum was formerly placed in Verbenaceae and is now classified in Lamiaceae following molecular revisions to Lamiales. Older references may still list Verbenaceae.</t>
+          <t>The spread here is relentless and very visible. New shoots come up from the roots faster than we can remove them, and offsets have crossed walkways into beds as far as twenty yards from the parent clump. It is too frequent to eradicate, so we manage it rather than chase it — look around and you will spot plants well outside their intended bed.</t>
         </is>
       </c>
       <c r="AB68" s="33" t="inlineStr">
@@ -12544,6 +12587,11 @@
       <c r="AC68" s="31" t="inlineStr">
         <is>
           <t>Standard</t>
+        </is>
+      </c>
+      <c r="AD68" s="45" t="inlineStr">
+        <is>
+          <t>NOMENCLATURE: Clerodendrum formerly Verbenaceae, now Lamiaceae (molecular Lamiales revision); older refs may list Verbenaceae. (Also in Origin.) RECLASSIFIED Green-&gt;Yellow/Watch List 2026-06-11 per Randy field obs: worst spreader in park, offsets cross walkways up to ~20 yds.</t>
         </is>
       </c>
     </row>
@@ -12586,10 +12634,10 @@
       <c r="H69" s="32" t="n"/>
       <c r="I69" s="33" t="inlineStr">
         <is>
-          <t>Few ornamental plants carry as much cultural weight. To Polynesian peoples the ti plant was sacred — associated with Lono, the god of agriculture. Planting ti at a home boundary was a statement of protection and prosperity. Carrying a ti leaf was believed to ward off evil spirits.
-The thick rhizomes are edible — baked until sweet or fermented into an alcoholic drink called okolehao in Hawaii. The leaves were used as food wrappers, rain capes, sandals, and hula skirts.
-The green-leaved form rarely sets seed and propagates almost exclusively by stem cutting. A stem section with a node, left on damp soil, will root. Hawaiian voyagers carried ti stems on long ocean passages and planted them at every new landfall.
-Toxic to dogs and cats despite being edible to people.</t>
+          <t>Carries immense cultural significance across Polynesia as a **sacred** symbol of protection, prosperity, and agriculture.
+A historical, multi-purpose plant: leaves were fashioned into garments and food wrappers, while the rhizomes were baked sweet for food or fermented into the Hawaiian spirit **okolehao**.
+The green-leaved form rarely sets seed and propagates almost exclusively by **stem cutting**. A stem section with a node, left on damp soil, will root. Hawaiian voyagers carried ti stems on long ocean passages and planted them at every new landfall.
+**Toxic to dogs and cats** despite being edible to people.</t>
         </is>
       </c>
       <c r="J69" s="33" t="inlineStr">
@@ -12600,35 +12648,38 @@
       <c r="K69" s="33" t="inlineStr">
         <is>
           <t>The ti plant was one of the most deliberately transported plants in human history. Polynesian voyagers carried stem cuttings on ocean passages of thousands of miles and planted them at every new landfall. By the time Europeans encountered the Pacific, ti was established from Southeast Asia through Melanesia, Micronesia, Polynesia, and Hawaii — a distribution almost entirely the result of human transport over centuries of migration.
-In Hawaiian culture the plant was sacred to Lono, god of agriculture and fertility. Planting ti along a home's boundary was a declaration of protection. Leaves were used for everything practical: food wrappers for imu (earth oven) cooking, rain capes, sandals, hula skirts, and lashing material. The rhizomes, high in fructose, were baked in an imu until sweet and edible, or fermented into okolehao, a traditional Hawaiian spirit.
-The green-leaved form rarely flowers or sets seed in cultivation. It is one of the most vegetatively reproduced plants known — a stem section with a node placed on damp soil will root reliably. This characteristic made it ideal as a voyaging plant: compact, indestructible in transit, and easily established on arrival.</t>
+In Hawaiian culture the plant was sacred to Lono, god of agriculture and fertility. Planting ti along a home's boundary was a declaration of protection. Leaves were used for everything practical: food wrappers for imu (earth oven) cooking, rain capes, sandals, hula skirts, and lashing material. The rhizomes were baked in an imu until sweet and edible, or fermented into okolehao, a traditional Hawaiian spirit. The sweetness is chemistry: the roots store energy as fructans (inulin-type polysaccharides) the body cannot digest raw, and long, slow baking breaks them down into simple, intensely sweet fructose — turning a fibrous, woody root into a high-calorie food.
+The green-leaved form rarely flowers or sets seed in cultivation. It is one of the most vegetatively reproduced plants known — a stem section with a node placed on damp soil will root reliably. This characteristic made it ideal as a voyaging plant: compact, indestructible in transit, and easily established on arrival.
+One note for modern gardeners: the brilliant pink, burgundy, and variegated ti plants common in Florida landscaping today are highly selected ornamental cultivars, not the plant the navigators carried. They tend to be more cold-tender than the rugged, deep-green ancestral ki, and the showiest forms can scorch in harsh direct sun — a reminder that the voyaging plant and the patio plant, though the same species, are not quite the same tool.</t>
         </is>
       </c>
       <c r="L69" s="33" t="inlineStr">
         <is>
-          <t>Limited direct wildlife value in Florida. The flowers, when they do appear, attract bees and occasionally hummingbirds. The berries are eaten by some birds.
-Primary value is cultural and historical rather than ecological. The plant's presence in the park collection is a connection to Pacific Island ethnobotany and the history of deliberate human plant migration across the ocean.</t>
+          <t>As an exotic species, it offers minimal ecological support to native Florida wildlife beyond occasional visitation by generalist pollinators. Its inclusion in the collection serves a primarily educational, ethnobotanical purpose.</t>
         </is>
       </c>
       <c r="M69" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Small, tubular, white to lavender-pink, in large branching clusters on a tall stalk. Rarely produced on the common green-leaved form in cultivation.
-Fruit — Small red to black berries. Rarely produced.
-Leaves — Long, strap-like, glossy green (standard form) or variously colored in ornamental cultivars (red, purple, cream, multicolored). Arranged in a rosette at the top of an unbranched cane-like stem.
-Rhizomes — Thick, fleshy, high in fructose. Edible when properly prepared. This is the part that gives rise to the spiritual and practical associations in Polynesian culture.
-Propagation — Stem cuttings root readily. The Hawaiian term for a stem cutting used for planting is a ki.
-What to Look For: The strap leaves in a crown at the top of a cane-like stem are distinctive. In the park, look for the unbranched stem with leaves clustered at the tip.</t>
+          <t>Flowers: Small, tubular, white to lavender-pink, in large branching clusters on a tall stalk. Rarely produced on the common green-leaved form in cultivation.
+Fruit: Small red to black berries. Rarely produced.
+Leaves: Long, strap-like (to about two feet), glossy green (standard form) or variously colored in ornamental cultivars (red, purple, cream, multicolored). Arranged in a rosette at the top of an unbranched cane-like stem.
+Rhizomes: Thick, fleshy, rich in fructans (inulin-type). Edible when properly prepared. This is the part that gives rise to the spiritual and practical associations in Polynesian culture.
+Propagation: Stem cuttings root readily. The Hawaiian term for a stem cutting used for planting is a ki.
+What to Look For: The strap leaves in a crown at the top of a cane-like stem are distinctive. In the park, look for the unbranched stem with leaves clustered at the tip. Not to be confused with the unrelated New Zealand cabbage tree (Cordyline australis).</t>
         </is>
       </c>
       <c r="N69" s="33" t="inlineStr">
         <is>
-          <t>An evergreen shrub or small tree, typically 3 to 10 feet tall, growing on slender, upright, cane-like stems. The strap-shaped leaves can reach roughly two feet long and come in green or, in cultivated forms, vivid reds, pinks, purples, and variegated blends.</t>
+          <t>Height/Length: 3 to 10 feet
+Habit: evergreen shrub or small tree; slender, upright, cane-like stems</t>
         </is>
       </c>
       <c r="O69" s="33" t="inlineStr">
         <is>
-          <t>A tropical plant that likes warmth, humidity, and rich, moist, well-drained soil. Green forms tolerate quite a bit of shade, while the colorful cultivars hold their best color in bright light. Hardy outdoors in USDA zones 10 to 11 (and sheltered spots in 9b); elsewhere it is a popular houseplant. Frost-sensitive.</t>
+          <t>Light: green forms tolerate shade; colorful cultivars need bright light for best color
+Soil: rich, moist, well-drained
+Humidity: likes warmth and humidity
+Cold tolerance: USDA zones 10 to 11 (sheltered 9b); frost-sensitive; houseplant elsewhere</t>
         </is>
       </c>
       <c r="P69" s="34" t="inlineStr">
@@ -12683,14 +12734,13 @@
       </c>
       <c r="Z69" s="33" t="inlineStr">
         <is>
-          <t>Also called Hawaiian ti, good luck plant, and ki or la'i (Hawaiian). Formerly known as Cordyline terminalis and, earlier, Convallaria fruticosa; older references place it in the lily family (Liliaceae) or in Agavaceae. Not to be confused with the unrelated Cordyline australis, the New Zealand "cabbage tree."</t>
-        </is>
-      </c>
-      <c r="AA69" s="33" t="inlineStr">
-        <is>
-          <t>NOMENCLATURE: Cordyline was formerly placed in Agavaceae and Laxmanniaceae; both are now subfamilies within Asparagaceae under the APG classification.</t>
-        </is>
-      </c>
+          <t>Hawaiian Ti
+Good Luck Plant
+Kī
+Lāʻī</t>
+        </is>
+      </c>
+      <c r="AA69" s="33" t="n"/>
       <c r="AB69" s="33" t="inlineStr">
         <is>
           <t>Culturally and Historically Significant</t>
@@ -12699,6 +12749,11 @@
       <c r="AC69" s="31" t="inlineStr">
         <is>
           <t>Feature</t>
+        </is>
+      </c>
+      <c r="AD69" s="45" t="inlineStr">
+        <is>
+          <t>NOMENCLATURE: Cordyline formerly Agavaceae/Laxmanniaceae; now subfamilies within Asparagaceae (APG). (Also in Origin.) MAINT/GENERATOR: badge shows skull Toxic because Dogs=Red, but rhizomes are a human food — add 'edible to people / toxic to pets' badge handling so cultural food plants don't carry a blanket Toxic skull. Applies to any edible-to-people + pet-toxic plant.</t>
         </is>
       </c>
     </row>
@@ -12741,10 +12796,10 @@
       <c r="H70" s="32" t="n"/>
       <c r="I70" s="33" t="inlineStr">
         <is>
-          <t>Florida has a genuine claim on this plant — it is native here, though its nativity within Florida is debated. Historically abundant in the Florida Keys and coastal hammocks; now rare in the wild here, though common in cultivation throughout the tropics.
-The national flower of the Bahamas and the official flower of the US Virgin Islands. The name esperanza — hope — is what it is called across much of Latin America.
-The seed pods are long, slender, and bean-like — the plant is in the bignonia family, not the bean family, but the pods look similar enough to cause confusion.
-Blooms heavily after rain, which makes it reliable in Florida's wet season.</t>
+          <t>Florida has a genuine claim on this plant — it is **native here**, though its nativity within Florida is debated. Historically abundant in the Florida Keys and coastal hammocks; now rare in the wild here, though common in cultivation throughout the tropics.
+The national flower of the Bahamas and the official flower of the US Virgin Islands. The name **esperanza** — hope — is what it is called across much of Latin America.
+The seed pods are long, slender, and bean-like — the plant is in the **bignonia family**, not the bean family, but the pods look similar enough to cause confusion.
+Blooms heavily **after rain**, which makes it reliable in Florida's wet season.</t>
         </is>
       </c>
       <c r="J70" s="33" t="inlineStr">
@@ -12756,7 +12811,9 @@
         <is>
           <t>Yellow Trumpet Flower is named the national flower of the Bahamas and the official flower of the US Virgin Islands — an unusual distinction for a plant that most Florida gardeners consider a common landscape shrub. Across Latin America it is called esperanza, meaning hope, an association with its tendency to bloom heavily after rain and its resilience in difficult conditions.
 Tecoma stans var. stans is classified as native to South Florida and the Keys by the Institute for Regional Conservation and the Florida Native Plant Society. It grows naturally in coastal hammocks and disturbed areas in Miami-Dade and Monroe counties and behaves ecologically as a Florida native throughout South and Central Florida.
-It is a documented butterfly nectar plant with a long bloom season, and the tubular yellow flowers are reliably visited by hummingbirds. The seed pods are long, slender, and woody — superficially bean-like but belonging to the Bignoniaceae family, not Fabaceae.</t>
+It is a documented butterfly nectar plant with a long bloom season, and the tubular yellow flowers are reliably visited by hummingbirds. The seed pods are long, slender, and woody — superficially bean-like but belonging to the Bignoniaceae family, not Fabaceae.
+There is a reason it seems to track the weather. After a dry spell the plant can look quiet and almost dormant, then flush into heavy bloom within days of a summer thunderstorm — its flowering pulses with the rains rather than the calendar. In Florida's wet season that makes it something close to a living rain gauge, brightest in the weeks the storms roll through.
+Look closely at the flowers and you may catch a bit of insect larceny. Hummingbirds and butterflies work the blooms the legitimate way, reaching down the tube and brushing past the pollen. Large native carpenter bees (Xylocopa), too bulky to push inside, often take a shortcut — chewing a small hole through the base of the flower to steal the nectar without touching the pollen at all. It is called nectar robbing, and once you spot the telltale slit at a flower's base, you start seeing it everywhere.</t>
         </is>
       </c>
       <c r="L70" s="33" t="inlineStr">
@@ -12767,22 +12824,27 @@
       </c>
       <c r="M70" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Bright yellow, tubular, five-lobed, in clusters at branch tips. Bloom period: nearly year-round in South Florida with peak flowering in warm months, especially after rain. Fast to reflower after pruning.
-Fruit and Seeds — Long, slender, woody seed pods, 4 to 8 inches long, superficially resembling bean pods. Seeds wind-dispersed when pods split. The plant self-seeds freely.
-Leaves — Opposite, pinnately compound with 5 to 13 leaflets. Medium green.
-Form — Fast-growing semi-evergreen shrub to small tree. Typically 3 to 6 feet as a shrub; can reach 15 to 25 feet as a multi-stemmed tree with age.
-What to Look For: The clusters of bright yellow tubular flowers at branch tips are unmistakable. The long slender seed pods hanging from branches after flowering. The pinnately compound leaves distinguish it from similarly yellow-flowered plants.</t>
+          <t>Flowers: Bright yellow, tubular, five-lobed, in clusters at branch tips. Bloom period: nearly year-round in South Florida with peak flowering in warm months, especially after rain. Fast to reflower after pruning.
+Fruit and Seeds: Long, slender, woody seed pods, 4 to 8 inches long, superficially resembling bean pods. Seeds wind-dispersed when pods split. The plant self-seeds freely.
+Leaves: Opposite, pinnately compound with 5 to 13 sharply toothed, lance-shaped leaflets. Medium green.
+Form: Fast-growing semi-evergreen shrub to small tree. Typically 3 to 6 feet as a shrub; can reach 10 to 20 feet as a multi-stemmed small tree with age.
+What to Look For: The clusters of bright yellow tubular flowers at branch tips are showy and distinctive. The long slender seed pods hang from branches after flowering. The pinnately compound leaves help distinguish it from similarly yellow-flowered plants — including the unrelated Tabebuia and Handroanthus trumpet trees.</t>
         </is>
       </c>
       <c r="N70" s="33" t="inlineStr">
         <is>
-          <t>A fast-growing semi-evergreen shrub to small tree, commonly 3 to 6 feet as a shrub but capable of reaching 10 to 20 feet or more as a multi-stemmed small tree. The compound leaves carry several sharply toothed, lance-shaped leaflets.</t>
+          <t>Height/Length: 3 to 6 feet as a shrub; 10 to 20 feet as a multi-stemmed small tree
+Habit: fast-growing semi-evergreen shrub to small tree</t>
         </is>
       </c>
       <c r="O70" s="33" t="inlineStr">
         <is>
-          <t>Loves heat and sun. It thrives in full sun and well-drained soil, is notably drought-tolerant and somewhat salt-tolerant once established, and copes with poor, rocky, or sandy ground. Best in USDA zones 9 to 11; in cooler spots it may die back in a freeze and resprout. Trimming spent flower clusters keeps it tidy and encourages more bloom.</t>
+          <t>Light: full sun
+Soil: well-drained; copes with poor, rocky, or sandy ground
+Drought tolerance: notably drought-tolerant once established
+Salt tolerance: somewhat salt-tolerant
+Cold tolerance: USDA zones 9 to 11; may die back in a freeze and resprout
+Note: trim spent flower clusters to keep it tidy and encourage more bloom</t>
         </is>
       </c>
       <c r="P70" s="34" t="inlineStr">
@@ -12837,7 +12899,11 @@
       </c>
       <c r="Z70" s="33" t="inlineStr">
         <is>
-          <t>Also called yellow elder, yellow bells, yellow trumpetbush, esperanza, and ginger-thomas. Carries old scientific synonyms including Bignonia stans (its original Linnaean name), Stenolobium stans, and Gelseminum stans. Its native-vs-introduced status in Florida is disputed. Can be confused with other yellow-flowered Bignoniaceae and with the unrelated Tabebuia and Handroanthus trumpet trees.</t>
+          <t>Yellow Elder
+Yellow Bells
+Yellow Trumpetbush
+Esperanza
+Ginger-Thomas</t>
         </is>
       </c>
       <c r="AA70" s="33" t="n"/>
@@ -12891,10 +12957,10 @@
       <c r="H71" s="32" t="n"/>
       <c r="I71" s="33" t="inlineStr">
         <is>
-          <t>Despite the name, this is not a climbing vine — it is a shrub. Most of its hundred-odd Thunbergia relatives are vigorous climbers. King's Mantle stayed low and bushy, which is why it is manageable in a garden setting where the climbing species are not.
-Deep purple flowers with a yellow throat, produced nearly continuously in warm conditions. One of the more reliable year-round bloomers in South Florida.
-Native to tropical West Africa. Member of Acanthaceae — the acanthus family.
-The common name honors its regal flower color. The genus name honors Carl Peter Thunberg, an 18th-century Swedish botanist who studied under Linnaeus and documented plants across Japan, South Africa, and Sri Lanka.</t>
+          <t>Despite the name, this is **not a climbing vine** — it is a shrub. Most of its hundred-odd Thunbergia relatives are vigorous climbers. King's Mantle stayed low and bushy, which is why it is manageable in a garden setting where the climbing species are not.
+**Deep purple** flowers with a yellow throat, produced nearly continuously in warm conditions. One of the more reliable year-round bloomers in South Florida.
+Native to tropical West Africa. Member of Acanthaceae — the **acanthus family**.
+The common name honors its regal flower color. The genus name honors **Carl Peter Thunberg**, an 18th-century Swedish botanist who studied under Linnaeus and documented plants across Japan, South Africa, and Sri Lanka.</t>
         </is>
       </c>
       <c r="J71" s="33" t="inlineStr">
@@ -12904,7 +12970,7 @@
       </c>
       <c r="K71" s="33" t="inlineStr">
         <is>
-          <t>King's Mantle is the well-behaved member of a mostly unruly genus. Most of the roughly 100 Thunbergia species are vigorous twining vines — the Sky Vine, Black-eyed Susan Vine, and Bengal Clock Vine are all relatives that will cover a fence or climb a tree if given the opportunity. King's Mantle stayed compact and shrubby, which makes it useful in a garden context where the climbing relatives are not.
+          <t>King's Mantle is the well-behaved member of a mostly unruly genus. Most of the roughly 100 Thunbergia species are vigorous twining vines — the Black-eyed Susan Vine and the Bengal Clock Vine (also called Sky Vine) are relatives that will cover a fence or climb a tree if given the opportunity. King's Mantle stayed compact and shrubby, which makes it useful in a garden context where the climbing relatives are not.
 The deep purple flowers with a contrasting yellow throat are produced nearly continuously through warm weather, making it one of the more reliable year-round flowering shrubs for Central and South Florida. The flower color is genuine — a saturated purple that holds up in full sun without fading to a washed-out lavender.
 The genus honors Carl Peter Thunberg, a Swedish botanist who studied under Linnaeus and conducted fieldwork in Japan, South Africa, and Sri Lanka in the 1770s and 1780s. His Flora Japonica (1784) was the first systematic treatment of Japanese plants by a European botanist.</t>
         </is>
@@ -12917,22 +12983,28 @@
       </c>
       <c r="M71" s="33" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Deep purple with a pale yellow throat, funnel-shaped, about 2 inches across. Produced singly at leaf axils in near-continuous succession through warm weather. The color is distinctive — genuine purple, not blue or lavender.
-Fruit — Small capsules. Not ornamentally significant.
-Leaves — Opposite, ovate to heart-shaped, medium green, with slightly wavy margins.
-Form — Evergreen shrub, typically 4 to 6 feet tall and 5 to 8 feet wide. Mounding, spreading habit. Does not climb.
+          <t>Flowers: Deep purple with a pale yellow throat, funnel-shaped, about 2 inches across. Produced singly at leaf axils in near-continuous succession through warm weather. The color is distinctive — genuine purple, not blue or lavender.
+Fruit: Small capsules. Not ornamentally significant.
+Leaves: Opposite, ovate to heart-shaped, medium green, with slightly wavy margins.
+Form: Evergreen shrub, typically 4 to 6 feet tall and 5 to 8 feet wide. Mounding, spreading habit. Does not climb.
 What to Look For: The deep purple flowers with yellow throats produced continuously along the branches are the year-round identification feature. The shrubby (non-climbing) habit distinguishes it from most other Thunbergia species.</t>
         </is>
       </c>
       <c r="N71" s="33" t="inlineStr">
         <is>
-          <t>An evergreen shrub, typically 4 to 6 feet tall and spreading 5 to 8 feet wide, with an upright, rounded, somewhat sprawling habit. Though usually grown as a bush, its stems will twine and climb if given support.</t>
+          <t>Height/Length: 4 to 6 feet
+Spread: 5 to 8 feet wide
+Habit: evergreen shrub; upright, rounded, somewhat sprawling. Unlike its vining relatives it does not twine, though loose stems can be trained on a support</t>
         </is>
       </c>
       <c r="O71" s="33" t="inlineStr">
         <is>
-          <t>Likes full sun to partial shade and moist, well-drained soil, and it blooms most freely in plenty of light. It is moderately drought-tolerant once established, fast-growing, and largely free of serious pests. Best in USDA zones 9 to 11; frost-tender but able to take brief dips near freezing. It responds well to pruning and makes a fine informal hedge, though heavy shearing reduces flowering.</t>
+          <t>Light: full sun to partial shade; blooms most freely in good light
+Soil: moist, well-drained
+Drought tolerance: moderate once established
+Growth rate: fast
+Cold tolerance: USDA zones 9 to 11; frost-tender but takes brief dips near freezing
+Note: responds well to pruning; a fine informal hedge, but heavy shearing reduces flowering</t>
         </is>
       </c>
       <c r="P71" s="34" t="inlineStr">
@@ -12942,7 +13014,7 @@
       </c>
       <c r="Q71" s="33" t="inlineStr">
         <is>
-          <t>Not an edible plant. Grown purely as an ornamental.</t>
+          <t>Not edible. Grown purely as an ornamental.</t>
         </is>
       </c>
       <c r="R71" s="34" t="inlineStr">
@@ -12987,10 +13059,15 @@
       </c>
       <c r="Z71" s="33" t="inlineStr">
         <is>
-          <t>Also called King's mantle, bush clockvine (or bush clock vine), and potato bush; a white-flowered cultivar exists. It is the shrubby, non-climbing member of a mostly vining genus and should not be confused with its climbing relatives, such as Thunbergia alata (black-eyed Susan vine) or the rampant Thunbergia grandiflora (Bengal trumpet / sky vine).</t>
-        </is>
-      </c>
-      <c r="AA71" s="33" t="n"/>
+          <t>Bush Clockvine
+Potato Bush</t>
+        </is>
+      </c>
+      <c r="AA71" s="33" t="inlineStr">
+        <is>
+          <t>Easy to walk right past. King's Mantle blooms quietly beside the Queen's Wreath, a taller, lusher vine that dominates the space and pulls the eye upward — so here, at least, the Queen rather outshines the King. Look low and close to the shrub's deep purple flowers and you will find it holding its own.</t>
+        </is>
+      </c>
       <c r="AB71" s="33" t="inlineStr">
         <is>
           <t>Flowering Shrubs and Vines</t>
@@ -13041,10 +13118,10 @@
       <c r="H72" s="32" t="n"/>
       <c r="I72" s="33" t="inlineStr">
         <is>
-          <t>Firebush is one of the most important native plants in South Florida for wildlife — hummingbirds, butterflies, and over 25 species of birds use it for nectar, fruit, or cover through the entire year.
-It blooms and fruits simultaneously, making it a multi-function wildlife station.
-Seminole people used the plant medicinally, applying crushed leaves to skin irritations.
-It grows fast, tolerates drought, and in frost-free areas becomes a sizeable shrub — one of the first recommendations any Florida naturalist makes for a wildlife-friendly yard.</t>
+          <t>Firebush is one of the most important **native plants** in South Florida for wildlife — hummingbirds, butterflies, and more than two dozen bird species use it for nectar, fruit, or cover through the entire year.
+It **blooms and fruits simultaneously**, making it a multi-function wildlife station.
+**Seminole** people used the plant medicinally, applying crushed leaves to skin irritations.
+It grows fast, tolerates drought, and in frost-free areas becomes a sizeable shrub — one of the first recommendations any Florida naturalist makes for a **wildlife-friendly yard**.</t>
         </is>
       </c>
       <c r="J72" s="33" t="inlineStr">
@@ -13054,7 +13131,8 @@
       </c>
       <c r="K72" s="33" t="inlineStr">
         <is>
-          <t>Firebush is one of the finest wildlife plants Florida has to offer — a genuine hummingbird and butterfly magnet. Its slim, bright orange-to-scarlet tubular flowers are perfectly shaped for the long bills and tongues of ruby-throated hummingbirds and bloom almost nonstop in warm weather; zebra longwings (Florida's state butterfly), gulf fritillaries, and sulphurs work the flowers all day, while mockingbirds, catbirds, and other songbirds gobble the juicy berries that ripen from green to red to purple-black. But firebush also comes wrapped in a cautionary tale that Florida native-plant lovers call "The Hamelia Mess." Most "firebush" sold in garden centers is not the native at all but a look-alike — Hamelia patens var. glabra, marketed as "African," "Dwarf," or "Compacta" firebush — which has smoother leaves and paler, more yellow-orange flowers and can interbreed with and genetically swamp wild native populations. So this unassuming shrub is both a beloved native wildlife powerhouse and a real lesson in why knowing exactly which plant you are planting matters.</t>
+          <t>For all its value, firebush comes wrapped in a cautionary tale that Florida native-plant lovers call “The Hamelia Mess.” Most “firebush” sold in garden centers is not the native at all but a look-alike, Hamelia patens var. glabra, marketed as “African,” “Dwarf,” or “Compacta” firebush. It has smoother leaves and paler, more yellow-orange flowers, and it can interbreed with and genetically swamp wild native populations. So this unassuming shrub is both a beloved native wildlife powerhouse and a real lesson in why knowing exactly which plant you are planting matters.
+Gardeners who want a more compact plant without the genetic risk can choose ‘Calusa,’ a true-native cultivar selected to stay small — the recommended alternative to the non-native dwarf forms.</t>
         </is>
       </c>
       <c r="L72" s="33" t="inlineStr">
@@ -13064,17 +13142,27 @@
       </c>
       <c r="M72" s="33" t="inlineStr">
         <is>
-          <t>Reproduces by seed, spread by the many birds that eat its berries, and is easily grown from cuttings. It blooms spring through fall — nearly year-round in frost-free spots — carrying clusters of narrow red-orange tubular flowers followed by berries that ripen through green, red, and finally purple-black. What to Look For: whorls of elliptical leaves with reddish veins and stalks, terminal clusters of slim orange-red trumpets, and strings of berries at several ripening stages on the same cluster. The native form is slightly fuzzy and often blushes red in cool weather.</t>
+          <t>Flowers: Clusters of narrow red-orange tubular flowers, spring through fall — nearly year-round in frost-free spots.
+Fruit: Berries ripen through green, red, and finally purple-black, often at several stages on the same cluster.
+Leaves: Whorls of elliptical leaves with reddish veins and stalks. The native form is slightly fuzzy and often blushes red in cool weather.
+Propagation: Reproduces by seed (spread by the many birds that eat its berries) and is easily grown from cuttings.
+What to Look For: Whorls of elliptical leaves with reddish veins, terminal clusters of slim orange-red trumpets, and strings of berries at several ripening stages on the same cluster.</t>
         </is>
       </c>
       <c r="N72" s="33" t="inlineStr">
         <is>
-          <t>In South Florida a fast-growing evergreen shrub to small tree that can reach 12 to 15 feet, though it is easily kept to 5 to 8 feet. In central and north Florida it behaves as a "root-hardy perennial," dying back in a freeze and resprouting from the roots in spring.</t>
+          <t>Height/Length: 12 to 15 feet (easily kept to 5 to 8 feet)
+Habit: fast-growing evergreen shrub to small tree; a root-hardy perennial in central and north Florida (dies back in a freeze, resprouts)</t>
         </is>
       </c>
       <c r="O72" s="33" t="inlineStr">
         <is>
-          <t>Tough and forgiving. It flowers best in full sun but tolerates partial shade (where it makes lusher foliage), grows in a wide range of well-drained soils, and is heat- and drought-tolerant once established with moderate salt tolerance — well suited to Florida-Friendly and pollinator gardens. Best in USDA zones 8 to 11; cold-sensitive at the top of the plant in cooler zones.</t>
+          <t>Light: full sun for best flowering; tolerates partial shade (lusher foliage)
+Soil: wide range, well-drained
+Drought tolerance: heat- and drought-tolerant once established
+Salt tolerance: moderate
+Cold tolerance: USDA zones 8 to 11; top cold-sensitive in cooler zones
+Note: well suited to Florida-Friendly and pollinator gardens</t>
         </is>
       </c>
       <c r="P72" s="39" t="inlineStr">
@@ -13119,7 +13207,7 @@
       </c>
       <c r="X72" s="30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Florida native; not invasive. Not on Florida's FISC invasive plant list.</t>
         </is>
       </c>
       <c r="Y72" s="36" t="inlineStr">
@@ -13129,7 +13217,10 @@
       </c>
       <c r="Z72" s="33" t="inlineStr">
         <is>
-          <t>Also called firebush, hummingbird bush, scarlet bush, redhead, and (in Belize) Ix Canaan, "Guardian of the Forest." The Florida native is Hamelia patens var. patens. Frequently confused with — and often sold as — the non-native Hamelia patens var. glabra ("African," "Dwarf," or "Compacta" firebush) and Hamelia cuprea ("Bahama" or Antillean firebush); a native compact cultivar, 'Calusa,' is the recommended small-size alternative. Florida growers call this look-alike problem "The Hamelia Mess."</t>
+          <t>Hummingbird Bush
+Scarlet Bush
+Redhead
+Ix Canaan</t>
         </is>
       </c>
       <c r="AA72" s="33" t="n"/>
@@ -13341,10 +13432,10 @@
       <c r="H74" s="40" t="n"/>
       <c r="I74" s="31" t="inlineStr">
         <is>
-          <t>The large yellow flower clusters and bold compound leaves make this one of the more visually assertive shrubs in the collection — hard to walk past without noticing.
-A member of the senna family (Fabaceae/Cassieae) and closely related to the Golden Shower Tree. The pods are large, four-winged, and distinctive.
-The leaves and seeds are toxic. Historically used as a medicinal plant throughout its native range in tropical America, with particular use as an antifungal skin treatment — the leaves were rubbed on ringworm infections, which is why it is also called Ringworm Bush.
-FISC Category II invasive in Florida — self-seeds freely and establishes in disturbed areas.</t>
+          <t>The large yellow flower clusters and bold compound leaves make this one of the more visually assertive shrubs in the collection — **hard to walk past** without noticing.
+A member of the senna family (Fabaceae/Cassieae) and closely related to the Golden Shower Tree. The pods are large, **four-winged**, and distinctive.
+The leaves and seeds are toxic. Historically used as a medicinal plant throughout its native range in tropical America, with particular use as an antifungal skin treatment — the leaves were rubbed on ringworm infections, which is why it is also called **Ringworm Bush**.
+**FISC Category I** invasive in Florida — Florida's highest invasive designation. Self-seeds freely and establishes in disturbed areas.</t>
         </is>
       </c>
       <c r="J74" s="31" t="inlineStr">
@@ -13356,7 +13447,7 @@
         <is>
           <t>Candelabra Bush is named for its flower spikes: stiff, upright spikes of bright yellow buds that open from the bottom up, standing above the foliage like rows of golden candles - the source of its other names, Emperor's Candlesticks and Christmas Candle. The bold, ladder-like compound leaves fold closed at night.
 Its oldest common name, Ringworm Bush, points to a long history in folk medicine: a crushed-leaf paste has been used across the tropics against ringworm and other fungal skin conditions, and the plant does contain compounds with documented antifungal activity. It is not, however, a plant to eat - the leaves and seeds contain anthraquinone glycosides and act as a strong laxative.
-It is a fast, short-lived tropical shrub from the Americas, now naturalized worldwide. In Florida it is a FISC Category II invasive that self-seeds freely, so it is kept and managed as an educational specimen rather than planted out.</t>
+It is a fast, short-lived tropical shrub from the Americas, now naturalized worldwide. In Florida it is a FISC Category I invasive — the state's highest designation — that self-seeds freely, so it is never one to plant near natural areas.</t>
         </is>
       </c>
       <c r="L74" s="31" t="inlineStr">
@@ -13367,12 +13458,11 @@
       </c>
       <c r="M74" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Bright yellow, five petals, in upright racemes at branch tips. Showy. Bloom over an extended season.
-Pods — Large, four-winged, distinctive — unlike most legume pods. Mature to brown and persist on the plant.
-Leaves — Large, pinnately compound with 8 to 14 pairs of leaflets. Bold texture.
-Form — Fast-growing shrub or small tree, 6 to 15 feet. Often multi-stemmed.
-What to Look For: The four-winged seed pods are unique and a reliable ID feature. The upright yellow flower clusters and large compound leaves are the visual signature when in bloom.</t>
+          <t>Flowers: Bright yellow, five petals, in upright racemes at branch tips. Showy. Bloom over an extended season.
+Pods: Large, four-winged, distinctive — unlike most legume pods. Mature to brown and persist on the plant.
+Leaves: Large, pinnately compound with 8 to 14 pairs of leaflets. Bold texture.
+Form: Fast-growing shrub or small tree, 6 to 12 feet. Often multi-stemmed.
+What to Look For: The four-winged seed pods are distinctive and a reliable ID feature. The upright yellow flower clusters and large compound leaves are the visual signature when in bloom.</t>
         </is>
       </c>
       <c r="N74" s="32" t="inlineStr">
@@ -13391,7 +13481,7 @@
 Drought tolerance: moderate
 Salt tolerance: moderate
 Cold tolerance: frost-tender; dies back in frost; USDA zones 9B to 11
-Note: a FISC Category II invasive that self-seeds heavily - deadhead spent spikes and remove volunteers; do not plant near natural areas.</t>
+Note: a FISC Category I invasive that self-seeds heavily - deadhead spent spikes and remove volunteers; do not plant near natural areas.</t>
         </is>
       </c>
       <c r="P74" s="38" t="inlineStr">
@@ -13436,7 +13526,7 @@
       </c>
       <c r="X74" s="31" t="inlineStr">
         <is>
-          <t>FISC Category II invasive in Florida. Self-seeds freely and establishes in disturbed areas. Do not plant near natural areas. Remove volunteers promptly.</t>
+          <t>FISC Category I invasive in Florida — the state's highest invasive designation. Self-seeds freely and establishes in disturbed areas. Do not plant near natural areas. Remove volunteers promptly.</t>
         </is>
       </c>
       <c r="Y74" s="44" t="inlineStr">
@@ -13451,7 +13541,11 @@
 Christmas Candle</t>
         </is>
       </c>
-      <c r="AA74" s="31" t="n"/>
+      <c r="AA74" s="31" t="inlineStr">
+        <is>
+          <t>The Candelabra Bush recorded at Palma Sola grew near the front gate, where all park observations date to 2024 and earlier. As a FISC Category I invasive it was targeted for removal — a stubborn one to clear — and as of 2025 we believe it has been fully taken out. A related Christmas senna still grows in the park's butterfly garden, where it makes a far better-behaved garden plant.</t>
+        </is>
+      </c>
       <c r="AB74" s="32" t="inlineStr">
         <is>
           <t>Plants to Watch and Invasive Awareness</t>
@@ -13460,6 +13554,11 @@
       <c r="AC74" s="31" t="inlineStr">
         <is>
           <t>Standard</t>
+        </is>
+      </c>
+      <c r="AD74" s="45" t="inlineStr">
+        <is>
+          <t>REMOVED specimen (front gate); last obs 2024; believed eradicated 2025. Published as species page for now, no QR sign planned. FISC corrected II-&gt;I per Randy 2026-06-11.</t>
         </is>
       </c>
     </row>
@@ -13502,10 +13601,10 @@
       <c r="H75" s="40" t="n"/>
       <c r="I75" s="31" t="inlineStr">
         <is>
-          <t>The flowers are orange-red, but the structure that makes this plant striking is the pagoda-like tiered arrangement of the flower clusters — each cluster stacked above the last in diminishing rings, like a Buddhist temple tower.
-A member of the mint family (Lamiaceae), confirmed by square stems. Related to the park's Turk's Turban and King's Mantle.
-Spreads aggressively by underground suckers. A single plant expands into a colony quickly. Worth knowing before siting it.
-Hummingbirds and butterflies work the flowers actively. A useful addition to a pollinator planting.</t>
+          <t>The flowers are orange-red, but the structure that makes this plant striking is the pagoda-like **tiered** arrangement of the flower clusters — each cluster stacked above the last in diminishing rings, like a Buddhist temple tower.
+A member of the mint family (Lamiaceae), confirmed by **square stems**. Related to the park's Starburst Bush and Turk's Turban.
+Spreads aggressively by **underground suckers**. A single plant expands into a colony quickly. Worth knowing before siting it.
+**Hummingbirds** and butterflies work the flowers actively. A useful addition to a pollinator planting.</t>
         </is>
       </c>
       <c r="J75" s="31" t="inlineStr">
@@ -13527,11 +13626,10 @@
       </c>
       <c r="M75" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Orange-red, tubular, in tiered pagoda-like whorls on upright stalks. The stacked arrangement is the defining visual feature.
-Leaves — Opposite, broadly ovate, medium green with slightly wavy margins.
-Form — Upright shrub, 4 to 8 feet. Spreads by underground suckers to form colonies. Square stems throughout.
-What to Look For: The tiered pagoda-like flower arrangement is unique — no other plant in the collection has this structure. Square stems confirm the mint family.</t>
+          <t>Flowers: Orange-red, tubular, in tiered pagoda-like whorls on upright stalks. The stacked arrangement is the defining visual feature.
+Leaves: Opposite, broadly ovate, medium green with slightly wavy margins.
+Form: Upright shrub, 3 to 6 feet. Spreads by underground suckers to form colonies. Square stems throughout.
+What to Look For: The tiered, pagoda-like flower arrangement is distinctive — stacked rings of bloom on an upright stalk. Square stems confirm the mint family.</t>
         </is>
       </c>
       <c r="N75" s="32" t="inlineStr">
@@ -13560,7 +13658,7 @@
       </c>
       <c r="Q75" s="31" t="inlineStr">
         <is>
-          <t>Not an edible plant.</t>
+          <t>Not edible. No food use documented.</t>
         </is>
       </c>
       <c r="R75" s="38" t="inlineStr">
@@ -13608,7 +13706,11 @@
           <t>Pagoda Clerodendrum</t>
         </is>
       </c>
-      <c r="AA75" s="31" t="n"/>
+      <c r="AA75" s="31" t="inlineStr">
+        <is>
+          <t>The Pagoda Flower recorded at Palma Sola grew on Welcome Island and was lost in the storms. The park's Tree Crinums have since expanded into that space, as they tend to do. All park observations predate the loss.</t>
+        </is>
+      </c>
       <c r="AB75" s="32" t="inlineStr">
         <is>
           <t>Flowering Shrubs and Vines</t>
@@ -13617,6 +13719,11 @@
       <c r="AC75" s="31" t="inlineStr">
         <is>
           <t>Standard</t>
+        </is>
+      </c>
+      <c r="AD75" s="45" t="inlineStr">
+        <is>
+          <t>REMOVED specimen (Welcome Island); storm loss; Tree Crinums took the space. Published as species page for now. Placeholder hero says 'help us photograph this' — mismatch for a gone plant; see §7 gone-plant placeholder decision.</t>
         </is>
       </c>
     </row>
@@ -13659,22 +13766,25 @@
       <c r="H76" s="40" t="n"/>
       <c r="I76" s="31" t="inlineStr">
         <is>
-          <t>One of the most medically significant plants in the world. Two alkaloids from this plant — vincristine and vinblastine — are used in chemotherapy for leukemia and Hodgkin's lymphoma. Madagascar periwinkle essentially transformed childhood leukemia from nearly always fatal to largely treatable.
-Despite that pharmaceutical pedigree, the plant itself is toxic and should not be eaten. The alkaloids that fight cancer in controlled pharmaceutical doses are harmful when ingested casually.
-Not native to Madagascar despite the name. Native to the Caribbean — probably Cuba.
-Blooms nearly year-round in Florida. One of the more heat and drought tolerant flowering plants available.</t>
+          <t>One of the most medically significant plants in the world — the source of **vincristine and vinblastine**, chemotherapy drugs used against leukemia and Hodgkin's lymphoma.
+A pharmaceutical powerhouse that is nonetheless **toxic** to eat, in every part. For admiring, not ingesting.
+Genuinely native to **Madagascar** — the name is accurate — though it has naturalized so widely across the tropics that many assume otherwise.
+Blooms nearly year-round in Florida, and ranks among the more **heat and drought tolerant** flowering plants available.</t>
         </is>
       </c>
       <c r="J76" s="31" t="inlineStr">
         <is>
-          <t>Non-native. Despite the common name, native to the Caribbean — likely Cuba and adjacent islands. Member of Apocynaceae — the dogbane family, same as oleander and plumeria.</t>
+          <t>Non-native. Native to Madagascar, where the genus Catharanthus is almost entirely endemic — the common name is apt. Naturalized widely across the Caribbean and the tropics. Member of Apocynaceae — the dogbane family, same as oleander and plumeria.</t>
         </is>
       </c>
       <c r="K76" s="32" t="inlineStr">
         <is>
-          <t>Madagascar Periwinkle is one of the most medically important plants in the world. Two alkaloids extracted from it - vincristine and vinblastine - became frontline chemotherapy drugs, and vincristine in particular helped turn childhood leukemia from a near-certain death sentence into a largely survivable disease. A common bedding plant carries one of modern medicine's quiet revolutions.
-The same chemistry makes the whole plant toxic to eat: it is for admiring, not ingesting. Despite the name it is not from Madagascar but the Caribbean, though it naturalized so thoroughly across the tropics that the misnomer stuck.
-It is tough and unfussy - blooming in heat, drought, and poor soil with flat, five-petaled pinwheel flowers in white, pink, or rose, often with a contrasting eye - which is exactly why it is so widely planted, and why it sometimes escapes into disturbed ground.</t>
+          <t>Madagascar Periwinkle is one of the most medically important plants in the world. Two alkaloids extracted from it - vincristine and vinblastine - became frontline chemotherapy drugs, and vincristine in particular helped turn childhood leukemia from a near-certain death sentence into a largely survivable disease.
+The way those drugs were found is a textbook case of scientific serendipity. In the 1950s, researchers at Eli Lilly and the University of Western Ontario were studying the plant not for cancer but for diabetes — folk medicine in places like Jamaica and the Philippines held that it lowered blood sugar. It did not. What they noticed instead was that it suppressed white blood cells, a dead end for diabetes that proved to be exactly the property needed against leukemia.
+The same chemistry makes the whole plant toxic to eat: it is for admiring, not ingesting. The name, for once, is accurate — it really is from Madagascar, where its genus is almost entirely endemic. It simply naturalized so thoroughly across the tropics that many people assume it came from somewhere closer to home.
+One naming wrinkle worth knowing: gardeners still call it vinca, a holdover from its old classification as Vinca rosea. Taxonomists later moved it into its own genus, Catharanthus — Greek for ‘pure flower.’ The nursery trade kept the familiar name; botany uses the precise one.
+It is tough and unfussy - blooming in heat, drought, and poor soil with flat, five-petaled pinwheel flowers in white, pink, or rose, often with a contrasting eye - which is exactly why it is so widely planted, and why it sometimes escapes into disturbed ground.
+This common landscape border plant is one of modern medicine's quietest triumphs — a contrast made sharper by the threatened status of its wild ancestors in Madagascar. The species is among the most widely planted bedding plants on Earth, yet its native populations have declined under pressure from slash-and-burn agriculture and charcoal production. A plant you can buy at any garden center is, in its true home, far less secure than its global ubiquity suggests.</t>
         </is>
       </c>
       <c r="L76" s="31" t="inlineStr">
@@ -13684,10 +13794,9 @@
       </c>
       <c r="M76" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Five flat petals forming a pinwheel, in white, pink, red, or lavender. A darker eye in the center. Produced nearly year-round.
-Leaves — Glossy, dark green, opposite, with a pale midrib. Evergreen.
-Form — Low, mounding, evergreen subshrub or annual, 1 to 2 feet tall. Freely branching.
+          <t>Flowers: Five flat petals forming a pinwheel, in white, pink, red, or lavender. A darker eye in the center. Produced nearly year-round.
+Leaves: Glossy, dark green, opposite, with a pale midrib. Evergreen.
+Form: Low, mounding, evergreen subshrub or annual, 1 to 2 feet tall. Freely branching.
 What to Look For: The flat five-petaled pinwheel flowers in various colors, the glossy leaves with pale midribs, and the very long bloom season are the identification package.</t>
         </is>
       </c>
@@ -13742,7 +13851,7 @@
       </c>
       <c r="V76" s="31" t="inlineStr">
         <is>
-          <t>Non-native. Native to the Caribbean.</t>
+          <t>Non-native. Native to Madagascar.</t>
         </is>
       </c>
       <c r="W76" s="38" t="inlineStr">
@@ -13776,6 +13885,12 @@
       <c r="AC76" s="31" t="inlineStr">
         <is>
           <t>Standard</t>
+        </is>
+      </c>
+      <c r="AD76" s="45" t="inlineStr">
+        <is>
+          <t>Conservation angle added (wild Madagascar decline: slash-and-burn + charcoal). IUCN category intentionally NOT stated as 'Critically Endangered' pending Randy verification — confirm Red List status to state precisely.
+Ethnobotanical thread available if wanted: plant was under study for folk ANTI-DIABETIC use when vinca alkaloids' effect on white blood cells was found serendipitously (could justify 'ethnobotanical' framing if Randy wants it expanded).</t>
         </is>
       </c>
     </row>
@@ -13845,11 +13960,10 @@
       </c>
       <c r="M77" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Tiny, cream-white, tubular, three per cluster, surrounded by three large colorful bracts. The bracts are the visual display.
-Bracts — The color display. Papery, in magenta, purple, red, orange, white, or bi-color depending on cultivar. Long-lasting.
-Spines — Recurved, sharp, along the stems. Handle with gloves.
-Form — Vigorous climbing or sprawling vine, 15 to 40 feet. Woody with age. Can be trained as a shrub with pruning.
+          <t>Flowers: Tiny, cream-white, tubular, three per cluster, surrounded by three large colorful bracts. The bracts are the visual display.
+Bracts: The color display. Papery, in magenta, purple, red, orange, white, or bi-color depending on cultivar. Long-lasting.
+Spines: Recurved, sharp, along the stems. Handle with gloves.
+Form: Vigorous climbing or sprawling vine, 15 to 40 feet. Woody with age. Can be trained as a shrub with pruning.
 What to Look For: The papery colored bracts in clusters are unmistakable. Look inside for the tiny cream flowers at the bract center. Handle stems with caution — the recurved spines are effective. The park's two bougainvilleas are easy to tell apart up close: this Great Bougainvillea has hairy, slightly velvety stems and leaves, while the Lesser Bougainvillea (Bougainvillea glabra, PSBP-00093) is nearly smooth.</t>
         </is>
       </c>
@@ -14011,10 +14125,9 @@
       </c>
       <c r="M78" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Pale blue to lavender with a yellow to white throat, trumpet-shaped, in hanging clusters (racemes). Up to 3 inches across. Produced over a long season.
-Leaves — Heart-shaped to triangular, medium green, on twining stems.
-Form — Vigorous twining vine, 20 to 30 feet or more. Woody with age. Not compact — this plant covers large areas.
+          <t>Flowers: Pale blue to lavender with a yellow to white throat, trumpet-shaped, in hanging clusters (racemes). Up to 3 inches across. Produced over a long season.
+Leaves: Heart-shaped to triangular, medium green, on twining stems.
+Form: Vigorous twining vine, 20 to 30 feet or more. Woody with age. Not compact — this plant covers large areas.
 What to Look For: The pale blue trumpets in drooping clusters are distinctive — few Florida vines offer this color. Compare with King's Mantle: same genus, completely different scale and habit.</t>
         </is>
       </c>
@@ -14176,11 +14289,10 @@
       </c>
       <c r="M79" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Pink to rose-purple, in rounded clusters. The flower structure is the milkweed signature: five reflexed petals with a central crown of five nectar-bearing horns. Bloom in summer.
-Fruit — Upright, elongated pods. Split at maturity to release seeds attached to silky white fibers (coma).
-Leaves — Opposite, lance-shaped, narrower than most milkweeds. Medium green.
-Form — Upright perennial, 2 to 4 feet tall. Dies back in winter — this is normal and desirable. Regrows from roots in spring.
+          <t>Flowers: Pink to rose-purple, in rounded clusters. The flower structure is the milkweed signature: five reflexed petals with a central crown of five nectar-bearing horns. Bloom in summer.
+Fruit: Upright, elongated pods. Split at maturity to release seeds attached to silky white fibers (coma).
+Leaves: Opposite, lance-shaped, narrower than most milkweeds. Medium green.
+Form: Upright perennial, 2 to 4 feet tall. Dies back in winter — this is normal and desirable. Regrows from roots in spring.
 What to Look For: The pink flower clusters in summer. Milky white sap from any broken stem — the milkweed family signature. Upright elongated pods in fall. Dies back in winter — the bare stems are not dead.</t>
         </is>
       </c>
@@ -14333,11 +14445,10 @@
       </c>
       <c r="M80" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Pale yellow, fragrant, appearing at the base of the leaf crown on the upper trunk. Male flowers on long branched stalks; female flowers on short stalks or sessile. Hermaphroditic cultivars bear both. Pollinated primarily by moths and bees.
-Fruit — Large, melon-like, borne directly on the trunk below the leaf crown. Green when immature, yellow to orange when ripe. Flesh orange to salmon. Center cavity contains black, peppery seeds in a gelatinous coating. Edible when ripe.
-Leaves — Very large, deeply palmate-lobed, on long hollow petioles. Arise in a crown at the top of the trunk. Drop progressively, leaving a ringed scar pattern on the trunk.
-Trunk — Soft, pithy, hollow, with prominent leaf scar rings. Exudes white latex when cut. Technically not woody — a giant herb.
+          <t>Flowers: Pale yellow, fragrant, appearing at the base of the leaf crown on the upper trunk. Male flowers on long branched stalks; female flowers on short stalks or sessile. Hermaphroditic cultivars bear both. Pollinated primarily by moths and bees.
+Fruit: Large, melon-like, borne directly on the trunk below the leaf crown. Green when immature, yellow to orange when ripe. Flesh orange to salmon. Center cavity contains black, peppery seeds in a gelatinous coating. Edible when ripe.
+Leaves: Very large, deeply palmate-lobed, on long hollow petioles. Arise in a crown at the top of the trunk. Drop progressively, leaving a ringed scar pattern on the trunk.
+Trunk: Soft, pithy, hollow, with prominent leaf scar rings. Exudes white latex when cut. Technically not woody — a giant herb.
 What to Look For: Fruit growing directly from the upper trunk is the defining feature. The deeply lobed leaf crown and ringed scar pattern on the trunk are visible year-round.</t>
         </is>
       </c>
@@ -14487,11 +14598,10 @@
       </c>
       <c r="M81" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Fronds — Bipinnate — divided twice — with the secondary leaflets having an irregular, ragged, fish-tail shaped margin. This is the definitive ID feature. No other common Florida palm has this leaf texture.
-Fruit — Round, dark red to black at maturity, in large hanging clusters. Produced once before the individual trunk dies. Toxic — handle with gloves.
-Trunk — Ringed, upright, clustering — multiple trunks from the same base. Individual trunks die after flowering.
-Form — Multi-stemmed clustering palm, 20 to 40 feet tall per stem.
+          <t>Fronds: Bipinnate — divided twice — with the secondary leaflets having an irregular, ragged, fish-tail shaped margin. This is the definitive ID feature. No other common Florida palm has this leaf texture.
+Fruit: Round, dark red to black at maturity, in large hanging clusters. Produced once before the individual trunk dies. Toxic — handle with gloves.
+Trunk: Ringed, upright, clustering — multiple trunks from the same base. Individual trunks die after flowering.
+Form: Multi-stemmed clustering palm, 20 to 40 feet tall per stem.
 What to Look For: The fish-tail leaflet shape is unmistakable — ragged-edged, irregular, unlike the smooth or toothed margins of other palms. Bipinnate frond structure (divided twice) distinguishes the whole Caryota genus.</t>
         </is>
       </c>
@@ -14646,11 +14756,10 @@
       </c>
       <c r="M82" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Fronds — Pinnate (feather-shaped), arching, with narrow leaflets. Similar in structure to other Phoenix palms.
-Fruit — Small, oval, orange-red to dark purple at maturity, in large hanging clusters. Edible but small and not commercially significant.
-Trunk — Multiple trunks from a shared base, leaning outward — the reclining habit. Each trunk is ringed and fiber-covered at the base.
-Form — Clustering palm, individual trunks 20 to 40 feet. The outward-leaning multiple trunks are the identification signature.
+          <t>Fronds: Pinnate (feather-shaped), arching, with narrow leaflets. Similar in structure to other Phoenix palms.
+Fruit: Small, oval, orange-red to dark purple at maturity, in large hanging clusters. Edible but small and not commercially significant.
+Trunk: Multiple trunks from a shared base, leaning outward — the reclining habit. Each trunk is ringed and fiber-covered at the base.
+Form: Clustering palm, individual trunks 20 to 40 feet. The outward-leaning multiple trunks are the identification signature.
 What to Look For: The multiple outward-leaning trunks from a common base distinguish this from single-trunk Phoenix palms. The small hanging fruit clusters when present.</t>
         </is>
       </c>
@@ -14807,11 +14916,10 @@
       </c>
       <c r="M83" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Fronds — Fan-shaped, divided nearly to the base into narrow segments. Produced in a spreading crown on each stem.
-Fruit — Small, black, berry-like.
-Trunk — Multiple, clustering, slender, ringed — resembling bamboo more than typical palm. Each stem wrapped in dark fiber at the base.
-Form — Dense clustering shrub to small palm, typically 6 to 12 feet tall. Slow-growing.
+          <t>Fronds: Fan-shaped, divided nearly to the base into narrow segments. Produced in a spreading crown on each stem.
+Fruit: Small, black, berry-like.
+Trunk: Multiple, clustering, slender, ringed — resembling bamboo more than typical palm. Each stem wrapped in dark fiber at the base.
+Form: Dense clustering shrub to small palm, typically 6 to 12 feet tall. Slow-growing.
 What to Look For: The fine-textured fan fronds and slender bamboo-like ringed stems in a dense cluster are distinctive. One of the few palms that thrives in significant shade.</t>
         </is>
       </c>
@@ -15133,11 +15241,10 @@
       </c>
       <c r="M85" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Very large, white, tubular opening to a broad bowl, up to 12 inches across. Open only at night, close and wilt by morning. Intensely fragrant. Bat and moth pollinated.
-Fruit — The commercial dragon fruit: oval, red-skinned with prominent green-tipped scales. White or magenta flesh with tiny black seeds. Sweet, mild flavor. Develops from pollinated flowers.
-Stems — Three-angled (triangular in cross-section), green, sprawling and climbing. Aerial roots along the stems attach to host surfaces. No true leaves — the green stems do all photosynthesis.
-Spines — Small, clustered at the notches along the stem angles. Less formidable than desert cacti.
+          <t>Flowers: Very large, white, tubular opening to a broad bowl, up to 12 inches across. Open only at night, close and wilt by morning. Intensely fragrant. Bat and moth pollinated.
+Fruit: The commercial dragon fruit: oval, red-skinned with prominent green-tipped scales. White or magenta flesh with tiny black seeds. Sweet, mild flavor. Develops from pollinated flowers.
+Stems: Three-angled (triangular in cross-section), green, sprawling and climbing. Aerial roots along the stems attach to host surfaces. No true leaves — the green stems do all photosynthesis.
+Spines: Small, clustered at the notches along the stem angles. Less formidable than desert cacti.
 What to Look For: The three-angled green climbing stems are the year-round marker. On a morning after blooming, look for wilted white flower remains. Ripe fruit hanging from stems is unmistakable if present.</t>
         </is>
       </c>
@@ -15291,10 +15398,9 @@
       </c>
       <c r="M86" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Small, inconspicuous, violet, on thin stalks above the rosette. Easy to miss.
-Seeds — Wind-dispersed, with hair-like fibers that catch on bark and wire to establish new plants.
-Form — Dense, rounded, gray-green rosettes 3 to 8 inches across. Grows in clusters on branches and wires throughout the park.
+          <t>Flowers: Small, inconspicuous, violet, on thin stalks above the rosette. Easy to miss.
+Seeds: Wind-dispersed, with hair-like fibers that catch on bark and wire to establish new plants.
+Form: Dense, rounded, gray-green rosettes 3 to 8 inches across. Grows in clusters on branches and wires throughout the park.
 What to Look For: The round gray-green rosettes on branches and wires throughout the park. Easily confused with Spanish moss at a glance — ball moss forms compact round clumps, Spanish moss forms hanging drapes.</t>
         </is>
       </c>
@@ -15448,11 +15554,10 @@
       </c>
       <c r="M87" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — White to cream, fragrant, five-petaled, in branching clusters. Attractive to bees. Produced nearly year-round in warm climates.
-Pods — Long, slender, three-sided, 12 to 18 inches long with constrictions at seed nodes — the drumstick appearance. Deep green when immature. The seeds inside are round with papery wings.
-Leaves — Tripinnate — leaflets of leaflets of leaflets — giving a delicate, feathery texture. Light to medium green. The compound structure is distinctive.
-Trunk — Whitish-gray, soft, with brittle branches that break easily in wind. Not a hardwood.
+          <t>Flowers: White to cream, fragrant, five-petaled, in branching clusters. Attractive to bees. Produced nearly year-round in warm climates.
+Pods: Long, slender, three-sided, 12 to 18 inches long with constrictions at seed nodes — the drumstick appearance. Deep green when immature. The seeds inside are round with papery wings.
+Leaves: Tripinnate — leaflets of leaflets of leaflets — giving a delicate, feathery texture. Light to medium green. The compound structure is distinctive.
+Trunk: Whitish-gray, soft, with brittle branches that break easily in wind. Not a hardwood.
 What to Look For: The feathery tripinnate leaves and the long slender three-sided pods hanging from branches are the definitive combination. The whitish soft trunk and brittle branches are secondary markers.</t>
         </is>
       </c>
@@ -15609,11 +15714,10 @@
       </c>
       <c r="M88" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Five overlapping petals in white, yellow, pink, or red depending on cultivar. The classic white-with-yellow-center form is most familiar. Intensely fragrant, especially in the evening. No nectar.
-Fruit — Rarely produced on cultivated trees. When present: paired elongated pods releasing winged seeds.
-Leaves — Large, oblong, dark glossy green, clustered at the tips of branches. Deciduous — drop in winter leaving bare blunt-tipped branches.
-Trunk and Branches — Thick, succulent, blunt-tipped. Exude white milky latex when cut or broken. The distinctive Y-branching pattern is recognizable at a distance.
+          <t>Flowers: Five overlapping petals in white, yellow, pink, or red depending on cultivar. The classic white-with-yellow-center form is most familiar. Intensely fragrant, especially in the evening. No nectar.
+Fruit: Rarely produced on cultivated trees. When present: paired elongated pods releasing winged seeds.
+Leaves: Large, oblong, dark glossy green, clustered at the tips of branches. Deciduous — drop in winter leaving bare blunt-tipped branches.
+Trunk and Branches: Thick, succulent, blunt-tipped. Exude white milky latex when cut or broken. The distinctive Y-branching pattern is recognizable at a distance.
 What to Look For: The Y-branching blunt-tipped form is visible year-round. In bloom, the flower clusters at branch tips are unmistakable. In winter, the bare blunt branches should not be mistaken for a dead tree.</t>
         </is>
       </c>
@@ -15767,10 +15871,9 @@
       </c>
       <c r="M89" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Small, blue-purple, tubular, in elongating spikes. Individual flowers open progressively from the base up the spike. Nearly continuous bloom.
-Leaves — Opposite, oval to ovate, with toothed margins. Medium green.
-Form — Sprawling to upright native wildflower, 2 to 4 feet. Can be leggy without pruning.
+          <t>Flowers: Small, blue-purple, tubular, in elongating spikes. Individual flowers open progressively from the base up the spike. Nearly continuous bloom.
+Leaves: Opposite, oval to ovate, with toothed margins. Medium green.
+Form: Sprawling to upright native wildflower, 2 to 4 feet. Can be leggy without pruning.
 What to Look For: The elongating blue-purple flower spikes are the primary feature. Watch for butterfly activity along the spikes. Distinguish from non-native Stachytarpheta jamaicensis by comparing leaf width — the native S. cayennensis has narrower leaves.</t>
         </is>
       </c>
@@ -15929,11 +16032,10 @@
       </c>
       <c r="M90" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Small, yellow, in racemes. Not ornamentally showy.
-Pods and Seeds — Spiny pods containing round, hard, gray seeds. Seeds are the ID confirmation — smooth, marble-like, distinctive.
-Stems — Scrambling, armed with recurved spines throughout. Handle with caution.
-Form — Scrambling to climbing spiny vine or sprawling shrub. Can form impenetrable thickets.
+          <t>Flowers: Small, yellow, in racemes. Not ornamentally showy.
+Pods and Seeds: Spiny pods containing round, hard, gray seeds. Seeds are the ID confirmation — smooth, marble-like, distinctive.
+Stems: Scrambling, armed with recurved spines throughout. Handle with caution.
+Form: Scrambling to climbing spiny vine or sprawling shrub. Can form impenetrable thickets.
 What to Look For: The recurved spines on the stems and pods are the first alert. The smooth round gray seeds inside the pods are unmistakable once you get past the spines to find them.</t>
         </is>
       </c>
@@ -16091,11 +16193,10 @@
       </c>
       <c r="M91" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Tiny, pale yellow-white to pink, in large upright panicles at branch tips. Produced in winter to early spring. Individually insignificant; collectively dramatic when a tree is in full bloom.
-Fruit — Variable by cultivar. Typically ovoid to kidney-shaped, 4 to 12 inches long. Skin green ripening to yellow, orange, or red. Flesh yellow to orange, juicy, sweet to tart. A large flat seed in the center.
-Leaves — Lanceolate, dark glossy green, reddish when new. Dense evergreen canopy.
-Trunk — Gray-brown, furrowed with age. Large specimens develop significant trunk diameter.
+          <t>Flowers: Tiny, pale yellow-white to pink, in large upright panicles at branch tips. Produced in winter to early spring. Individually insignificant; collectively dramatic when a tree is in full bloom.
+Fruit: Variable by cultivar. Typically ovoid to kidney-shaped, 4 to 12 inches long. Skin green ripening to yellow, orange, or red. Flesh yellow to orange, juicy, sweet to tart. A large flat seed in the center.
+Leaves: Lanceolate, dark glossy green, reddish when new. Dense evergreen canopy.
+Trunk: Gray-brown, furrowed with age. Large specimens develop significant trunk diameter.
 What to Look For: The dense dark canopy and the flower panicles in winter are the best seasonal markers. Ripe fruit hanging from branches is unmistakable. New reddish leaf growth at branch tips is visible when trees flush.</t>
         </is>
       </c>
@@ -16248,11 +16349,10 @@
       </c>
       <c r="M92" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Rounded heads of numerous long pink stamens — no visible petals. Powder-puff appearance. Produced nearly year-round.
-Leaves — Bipinnate, with small leaflets, giving a fine-textured appearance.
-Pods — Flat, legume-style, splitting explosively at maturity.
-Form — Compact evergreen shrub, 3 to 6 feet tall and wide.
+          <t>Flowers: Rounded heads of numerous long pink stamens — no visible petals. Powder-puff appearance. Produced nearly year-round.
+Leaves: Bipinnate, with small leaflets, giving a fine-textured appearance.
+Pods: Flat, legume-style, splitting explosively at maturity.
+Form: Compact evergreen shrub, 3 to 6 feet tall and wide.
 What to Look For: The pink staminal powder-puff heads are unmistakable. The fine bipinnate foliage is the secondary marker.</t>
         </is>
       </c>
@@ -16413,10 +16513,9 @@
       </c>
       <c r="M93" s="32" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers - Small, three-petaled, pink to magenta, at the stem tips, opening in the morning.
-Leaves - Lance-shaped, fleshy, deep purple, clasping the jointed stems.
-Form - Low, trailing, brittle-stemmed groundcover that roots at the nodes.
+          <t>Flowers: Small, three-petaled, pink to magenta, at the stem tips, opening in the morning.
+Leaves: Lance-shaped, fleshy, deep purple, clasping the jointed stems.
+Form: Low, trailing, brittle-stemmed groundcover that roots at the nodes.
 What to Look For: A spreading mat of saturated purple stems and leaves topped by small pink flowers - the color is unmistakable. Stems snap easily and root where they land.</t>
         </is>
       </c>
@@ -16572,11 +16671,10 @@
       </c>
       <c r="M94" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Tiny, cream-white, tubular, three per cluster, inside the colorful bracts.
-Bracts — Papery, long-lasting, in purple, magenta, pink, white, or orange. The visual display of the plant.
-Spines — Recurved, along stems. Handle with gloves.
-Form — Vigorous climbing or sprawling vine. Can be trained as a shrub with pruning.
+          <t>Flowers: Tiny, cream-white, tubular, three per cluster, inside the colorful bracts.
+Bracts: Papery, long-lasting, in purple, magenta, pink, white, or orange. The visual display of the plant.
+Spines: Recurved, along stems. Handle with gloves.
+Form: Vigorous climbing or sprawling vine. Can be trained as a shrub with pruning.
 What to Look For: The papery bracts are the signature. Look for the tiny true flowers inside the bract cluster. Stems are armed with recurved spines.</t>
         </is>
       </c>
@@ -16728,11 +16826,10 @@
       </c>
       <c r="M95" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Bright blue (standard) or white, with a distinctive gold and white center marking. Up to 2 inches across. Produced along the twining stems over a long season.
-Pods — Flat, elongated legume pods. Seeds dark.
-Leaves — Pinnately compound with three to nine leaflets.
-Form — Twining vine, 6 to 10 feet. Climbs readily on any support.
+          <t>Flowers: Bright blue (standard) or white, with a distinctive gold and white center marking. Up to 2 inches across. Produced along the twining stems over a long season.
+Pods: Flat, elongated legume pods. Seeds dark.
+Leaves: Pinnately compound with three to nine leaflets.
+Form: Twining vine, 6 to 10 feet. Climbs readily on any support.
 What to Look For: The vivid blue flowers with the gold center marking are unmistakable — few plants in Florida offer this color. The three-leaflet compound leaves on a twining stem are the secondary ID.</t>
         </is>
       </c>
@@ -16887,10 +16984,9 @@
       </c>
       <c r="M96" s="32" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers - Small, white, three-petaled, clustered low among the leaves inside a pair of boat-shaped purple bracts.
-Leaves - Stiff, sword-shaped, in a rosette; glossy green above, deep purple beneath.
-Form - Low, clumping rosette groundcover, spreading into colonies.
+          <t>Flowers: Small, white, three-petaled, clustered low among the leaves inside a pair of boat-shaped purple bracts.
+Leaves: Stiff, sword-shaped, in a rosette; glossy green above, deep purple beneath.
+Form: Low, clumping rosette groundcover, spreading into colonies.
 What to Look For: Rosettes of two-toned green-and-purple sword leaves; look down at the leaf bases for the little white flowers nested in purple boat-shaped bracts.</t>
         </is>
       </c>
@@ -17045,11 +17141,10 @@
       </c>
       <c r="M97" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Small, pink, five-petaled, produced in small clusters. Attractive to bees.
-Fruit — Small, round to slightly lobed, bright red when ripe. Similar in appearance to a small cherry. Produced nearly year-round in Florida conditions.
-Leaves — Opposite, oval, glossy dark green. Evergreen.
-Form — Shrub to small tree, 6 to 15 feet. Dense, rounded canopy.
+          <t>Flowers: Small, pink, five-petaled, produced in small clusters. Attractive to bees.
+Fruit: Small, round to slightly lobed, bright red when ripe. Similar in appearance to a small cherry. Produced nearly year-round in Florida conditions.
+Leaves: Opposite, oval, glossy dark green. Evergreen.
+Form: Shrub to small tree, 6 to 15 feet. Dense, rounded canopy.
 What to Look For: The small red cherry-like fruit on a dense evergreen shrub is the primary identification feature. The fruit is soft, juicy, and highly tart when ripe.</t>
         </is>
       </c>
@@ -17206,11 +17301,10 @@
       </c>
       <c r="M98" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — White, star-shaped, with long exserted purple stamens. Open in the evening, most visually striking at dusk and in low light. Fragrant. Produced over a long season.
-Fruit — Small, glossy, purple-black berries enclosed in a persistent red-purple calyx. Ornamentally attractive. Eaten by birds.
-Leaves — Large, opposite, dark glossy green, ovate with a pointed tip. Stems square in cross-section — mint family signature.
-Form — Evergreen to semi-evergreen shrub, 6 to 10 feet tall. Spreads aggressively by underground suckers. Can form large colonies.
+          <t>Flowers: White, star-shaped, with long exserted purple stamens. Open in the evening, most visually striking at dusk and in low light. Fragrant. Produced over a long season.
+Fruit: Small, glossy, purple-black berries enclosed in a persistent red-purple calyx. Ornamentally attractive. Eaten by birds.
+Leaves: Large, opposite, dark glossy green, ovate with a pointed tip. Stems square in cross-section — mint family signature.
+Form: Evergreen to semi-evergreen shrub, 6 to 10 feet tall. Spreads aggressively by underground suckers. Can form large colonies.
 What to Look For: Visit at dusk — this is the plant at its best. The white star flowers with purple stamens against dark foliage are distinctive. The red-purple calyces holding the dark berries are visible year-round on mature plants. Square stems confirm mint family membership.</t>
         </is>
       </c>
@@ -17360,11 +17454,10 @@
       </c>
       <c r="M99" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Bright yellow, pea-shaped, in large upright clusters. Showy and produced over a long season.
-Pods — The ID feature: tightly constricted between each seed, creating a beaded or necklace appearance. Distinctive.
-Leaves — Pinnately compound with oval leaflets. Silvery-gray-green, giving a soft texture.
-Form — Rounded evergreen shrub, 6 to 12 feet tall and wide. Salt and drought tolerant.
+          <t>Flowers: Bright yellow, pea-shaped, in large upright clusters. Showy and produced over a long season.
+Pods: The ID feature: tightly constricted between each seed, creating a beaded or necklace appearance. Distinctive.
+Leaves: Pinnately compound with oval leaflets. Silvery-gray-green, giving a soft texture.
+Form: Rounded evergreen shrub, 6 to 12 feet tall and wide. Salt and drought tolerant.
 What to Look For: The constricted necklace-bead pods are unmistakable when present. The silvery compound foliage and yellow flower clusters are the seasonal markers.</t>
         </is>
       </c>
@@ -17519,10 +17612,9 @@
       </c>
       <c r="M100" s="32" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers - Pink, funnel-shaped, crocus-like, 2 to 3 inches across, held singly on short stalks; appearing in flushes a few days after heavy rain.
-Leaves - Narrow, grassy, dark green, from an underground bulb.
-Form - Low clumping bulb; spreads by offsets and seed.
+          <t>Flowers: Pink, funnel-shaped, crocus-like, 2 to 3 inches across, held singly on short stalks; appearing in flushes a few days after heavy rain.
+Leaves: Narrow, grassy, dark green, from an underground bulb.
+Form: Low clumping bulb; spreads by offsets and seed.
 What to Look For: Sudden flushes of pink crocus-like flowers over grassy foliage in the days after a summer downpour. Between rains, an unremarkable grassy clump.</t>
         </is>
       </c>
@@ -17679,11 +17771,10 @@
       </c>
       <c r="M101" s="32" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers - Large, showy, yellow, pea-shaped, about an inch across, in tall upright spikes, mainly late summer to fall.
-Pods and Seeds - Cylindrical, inflated, ripening brown; dry seeds rattle inside. The ID confirmation.
-Leaves - Simple (single, not divided), broadest near the tip - distinct from the trifoliate leaves of Smooth Rattlebox.
-Form - Erect annual herb, 1.5 to 6 feet tall.
+          <t>Flowers: Large, showy, yellow, pea-shaped, about an inch across, in tall upright spikes, mainly late summer to fall.
+Pods and Seeds: Cylindrical, inflated, ripening brown; dry seeds rattle inside. The ID confirmation.
+Leaves: Simple (single, not divided), broadest near the tip - distinct from the trifoliate leaves of Smooth Rattlebox.
+Form: Erect annual herb, 1.5 to 6 feet tall.
 What to Look For: Tall stems of large yellow pea flowers with single (not three-part) leaves, followed by inflated rattling pods. The simple leaf separates it from Smooth Rattlebox.</t>
         </is>
       </c>
@@ -17834,11 +17925,10 @@
       </c>
       <c r="M102" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Small, tubular, in rounded clusters. Each cluster contains flowers of multiple ages and therefore multiple colors simultaneously — yellow, orange, pink, and red on one cluster.
-Fruit — Small, round, green ripening to purple-black. Green berries toxic; ripe berries eaten by birds.
-Leaves — Rough, opposite, strongly aromatic when crushed. The scent is distinctive and not universally liked.
-Form — Sprawling to mounding shrub, variable height. Aggressive grower.
+          <t>Flowers: Small, tubular, in rounded clusters. Each cluster contains flowers of multiple ages and therefore multiple colors simultaneously — yellow, orange, pink, and red on one cluster.
+Fruit: Small, round, green ripening to purple-black. Green berries toxic; ripe berries eaten by birds.
+Leaves: Rough, opposite, strongly aromatic when crushed. The scent is distinctive and not universally liked.
+Form: Sprawling to mounding shrub, variable height. Aggressive grower.
 What to Look For: The multi-colored flower clusters — multiple colors simultaneously on one head — are the most reliable ID feature. The strongly aromatic rough-textured leaves confirm it. The green and purple-black fruit together on the same plant.</t>
         </is>
       </c>
@@ -17992,11 +18082,10 @@
       </c>
       <c r="M103" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Brilliant red, five-petaled, with a prominent staminal column. Appear in late winter on bare leafless branches. Produced in abundance — a flowering tree is one of the more striking sights in the park in late winter.
-Fruit and Seeds — Woody capsules releasing masses of white cottony fiber containing the seeds. Birds collect the fiber for nesting.
-Leaves — Palmate compound, with 5 to 7 leaflets. Deciduous — the tree is bare in winter when it flowers.
-Trunk — Gray-green with large conical spines on trunk and major branches — same defensive strategy as the adjacent Kapok. Develops buttressing at the base with age.
+          <t>Flowers: Brilliant red, five-petaled, with a prominent staminal column. Appear in late winter on bare leafless branches. Produced in abundance — a flowering tree is one of the more striking sights in the park in late winter.
+Fruit and Seeds: Woody capsules releasing masses of white cottony fiber containing the seeds. Birds collect the fiber for nesting.
+Leaves: Palmate compound, with 5 to 7 leaflets. Deciduous — the tree is bare in winter when it flowers.
+Trunk: Gray-green with large conical spines on trunk and major branches — same defensive strategy as the adjacent Kapok. Develops buttressing at the base with age.
 What to Look For: In late winter, the red flowers on bare branches are visible from across the park. Year-round, the spiny trunk and the proximity to the Kapok and Baobab make this easy to locate. Compare trunk spines between the Red Silk Cotton and the Kapok side by side.</t>
         </is>
       </c>
@@ -18146,10 +18235,9 @@
       </c>
       <c r="M104" s="32" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers - Tiny, white to greenish, in small rounded clusters on short stalks.
-Leaves - Round, glossy, scalloped at the edge, 1 to 2 inches across, with the stalk attached at the center of the leaf (peltate) - the key ID feature.
-Form - Low, creeping, mat-forming; spreads by rhizomes at and just below the surface.
+          <t>Flowers: Tiny, white to greenish, in small rounded clusters on short stalks.
+Leaves: Round, glossy, scalloped at the edge, 1 to 2 inches across, with the stalk attached at the center of the leaf (peltate) - the key ID feature.
+Form: Low, creeping, mat-forming; spreads by rhizomes at and just below the surface.
 What to Look For: Round, coin-like leaves on central stalks forming a low mat in wet ground or at the pond edge. The center-attached leaf stalk separates it from similar weeds.</t>
         </is>
       </c>
@@ -18304,11 +18392,10 @@
       </c>
       <c r="M105" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Small, white, tubular, in clusters. Produced in spring and summer.
-Fruit — Small, round, red ripening to black. Two-seeded. Produced in clusters. Edible but not significant as a food plant.
-Leaves — Opposite, glossy dark green, with deeply impressed veins giving a quilted or corrugated appearance. This is the year-round ID feature.
-Form — Evergreen shrub, 4 to 15 feet, depending on light conditions. Shade-tolerant.
+          <t>Flowers: Small, white, tubular, in clusters. Produced in spring and summer.
+Fruit: Small, round, red ripening to black. Two-seeded. Produced in clusters. Edible but not significant as a food plant.
+Leaves: Opposite, glossy dark green, with deeply impressed veins giving a quilted or corrugated appearance. This is the year-round ID feature.
+Form: Evergreen shrub, 4 to 15 feet, depending on light conditions. Shade-tolerant.
 What to Look For: The deeply veined, glossy, corrugated-looking dark green leaves are distinctive year-round. No other common native Florida shrub has quite this leaf texture. Red to black berry clusters when fruiting.</t>
         </is>
       </c>
@@ -18456,11 +18543,10 @@
       </c>
       <c r="M106" s="32" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers - Tiny, white, star-shaped, in tight clusters (whorls) at the leaf nodes along the stem.
-Fruit - Small dry capsules; reproduces by seed.
-Leaves - Narrow, opposite, rough-textured, often with clusters of smaller leaves in the axils.
-Form - Low, many-branched, weakly woody-based groundcover.
+          <t>Flowers: Tiny, white, star-shaped, in tight clusters (whorls) at the leaf nodes along the stem.
+Fruit: Small dry capsules; reproduces by seed.
+Leaves: Narrow, opposite, rough-textured, often with clusters of smaller leaves in the axils.
+Form: Low, many-branched, weakly woody-based groundcover.
 What to Look For: Whorls of tiny white flowers tucked where the narrow leaves meet the stem, low in disturbed ground. Look for small bees and wasps working the flowers.</t>
         </is>
       </c>
@@ -18612,13 +18698,11 @@
       </c>
       <c r="M107" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Trumpet-shaped, in pink, red, yellow, white, or bi-color. Open late afternoon, close mid-morning. Fragrant in the evening.
-Fruit — Small, dark, angular achene-like fruits. Each flower produces one.
-Leaves — Opposite, ovate, smooth, medium green.
-Form — Bushy perennial, 2 to 4 feet tall. Dies back to a large tuberous root in cold weather; resprouts in spring.
-What to Look For: Closed in the morning, open by mid-afternoon — the timing is the easiest confirmation. The trumpet flowers in mixed colors on a bushy plant. The evening fragrance when flowers are open.
-What to Look For: Visit in the morning and find tightly furled tubes. Return after 4 PM and find them fully open and fragrant. The timing is reliable.</t>
+          <t>Flowers: Trumpet-shaped, in pink, red, yellow, white, or bi-color. Open late afternoon, close mid-morning. Fragrant in the evening.
+Fruit: Small, dark, angular achene-like fruits. Each flower produces one.
+Leaves: Opposite, ovate, smooth, medium green.
+Form: Bushy perennial, 2 to 4 feet tall. Dies back to a large tuberous root in cold weather; resprouts in spring.
+What to Look For: Visit in the morning and find the flowers tightly furled into tubes; return after 4 PM and find them fully open and fragrant. That daily timing is the easiest confirmation. Look for trumpet flowers in mixed colors — pink, red, yellow, white, often on the same plant — on a bushy, 2-to-4-foot perennial.</t>
         </is>
       </c>
       <c r="N107" s="32" t="inlineStr">
@@ -18768,10 +18852,9 @@
       </c>
       <c r="M108" s="32" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers - Bright yellow to yellow-orange, daisy-like, about 1 inch across, held singly on short stalks above the foliage. Nearly year-round.
-Leaves - Fleshy, glossy, dark green, usually three-lobed, 2 to 4 inches long, with toothed margins.
-Form - Low, mat-forming perennial; rounded stems root at the nodes as they creep.
+          <t>Flowers: Bright yellow to yellow-orange, daisy-like, about 1 inch across, held singly on short stalks above the foliage. Nearly year-round.
+Leaves: Fleshy, glossy, dark green, usually three-lobed, 2 to 4 inches long, with toothed margins.
+Form: Low, mat-forming perennial; rounded stems root at the nodes as they creep.
 What to Look For: A dense mat of glossy three-lobed leaves studded with yellow daisies. Compare with the native Beach Sunflower - similar flower, very different plant and behavior.</t>
         </is>
       </c>
@@ -18925,10 +19008,9 @@
       </c>
       <c r="M109" s="32" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers - Small, star-shaped, white to pink or lavender, about a third of an inch across, clustered at the branch tips. Long blooming, heaviest fall through winter.
-Leaves - Opposite, hairy, narrowly elliptical, tapering at both ends.
-Form - Low, creeping perennial with hairy branching stems that root at the nodes, forming mats.
+          <t>Flowers: Small, star-shaped, white to pink or lavender, about a third of an inch across, clustered at the branch tips. Long blooming, heaviest fall through winter.
+Leaves: Opposite, hairy, narrowly elliptical, tapering at both ends.
+Form: Low, creeping perennial with hairy branching stems that root at the nodes, forming mats.
 What to Look For: Mats of small star-shaped white-to-pink flowers in thin turf and sandy disturbed ground, busiest with small pollinators in the cooler months.</t>
         </is>
       </c>
@@ -19079,10 +19161,9 @@
       </c>
       <c r="M110" s="32" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers - Tiny, white with a yellow lip, in a short compact spike a few inches tall, mainly in winter and early spring.
-Leaves - Narrow, grass-like to lance-shaped, in a small low rosette, often with a slight reddish tinge.
-Form - A small terrestrial orchid, only a few inches tall, appearing seasonally in lawns and damp open turf.
+          <t>Flowers: Tiny, white with a yellow lip, in a short compact spike a few inches tall, mainly in winter and early spring.
+Leaves: Narrow, grass-like to lance-shaped, in a small low rosette, often with a slight reddish tinge.
+Form: A small terrestrial orchid, only a few inches tall, appearing seasonally in lawns and damp open turf.
 What to Look For: In winter, scan short grass for a small rosette topped by a stubby spike of little white-and-yellow flowers. Easy to miss and easy to mow over.</t>
         </is>
       </c>
@@ -19235,11 +19316,10 @@
       </c>
       <c r="M111" s="32" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers - Yellow, pea-shaped, in upright clusters (racemes) at the stem tips, often streaked with fine reddish-brown lines.
-Pods and Seeds - Green ripening to brown, swollen and inflated; the dry seeds rattle inside. The ID confirmation.
-Leaves - Compound, each with three oval leaflets (trifoliate).
-Form - Erect, branching annual to short-lived perennial herb, woody at the base.
+          <t>Flowers: Yellow, pea-shaped, in upright clusters (racemes) at the stem tips, often streaked with fine reddish-brown lines.
+Pods and Seeds: Green ripening to brown, swollen and inflated; the dry seeds rattle inside. The ID confirmation.
+Leaves: Compound, each with three oval leaflets (trifoliate).
+Form: Erect, branching annual to short-lived perennial herb, woody at the base.
 What to Look For: Upright stems of yellow pea flowers above three-part leaves, followed by inflated pods that rattle when shaken. Look for the brightly colored Bella Moth or its caterpillars on the plant.</t>
         </is>
       </c>
@@ -19392,10 +19472,9 @@
       </c>
       <c r="M112" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Small, pale pink to rose, five-petaled. Produced continuously on new growth. Less showy than ornamental hibiscus relatives.
-Leaves — Deeply lobed, burgundy-red throughout, with a metallic sheen. The color is the definitive identification feature.
-Form — Upright to sprawling shrub, 4 to 8 feet in warm conditions. May die back in frost; regrows from roots.
+          <t>Flowers: Small, pale pink to rose, five-petaled. Produced continuously on new growth. Less showy than ornamental hibiscus relatives.
+Leaves: Deeply lobed, burgundy-red throughout, with a metallic sheen. The color is the definitive identification feature.
+Form: Upright to sprawling shrub, 4 to 8 feet in warm conditions. May die back in frost; regrows from roots.
 What to Look For: The deep burgundy-red lobed leaves are unmistakable — no other common Florida shrub has this color with this leaf shape. The small pink flowers are secondary.</t>
         </is>
       </c>
@@ -19548,11 +19627,10 @@
       </c>
       <c r="M113" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Lavender-pink to purple, with five petals, one marked with a deeper color stripe. Up to 4 inches across. Produced in late winter to early spring, often before the tree fully leafs out.
-Fruit — Long, flat, woody legume pods, 8 to 12 inches long. Twist and split explosively at maturity to disperse seeds. Produced in abundance.
-Leaves — The defining feature: two-lobed, each lobe rounded, split at the tip. The outline resembles a butterfly or a camel's footprint. Medium green, smooth.
-Form — Semi-deciduous small to medium tree, typically 20 to 35 feet. Open, spreading canopy.
+          <t>Flowers: Lavender-pink to purple, with five petals, one marked with a deeper color stripe. Up to 4 inches across. Produced in late winter to early spring, often before the tree fully leafs out.
+Fruit: Long, flat, woody legume pods, 8 to 12 inches long. Twist and split explosively at maturity to disperse seeds. Produced in abundance.
+Leaves: The defining feature: two-lobed, each lobe rounded, split at the tip. The outline resembles a butterfly or a camel's footprint. Medium green, smooth.
+Form: Semi-deciduous small to medium tree, typically 20 to 35 feet. Open, spreading canopy.
 What to Look For: The two-lobed leaves are the reliable year-round marker — no other common Florida tree has this leaf shape. In late winter, the lavender-pink flowers are distinctive. Compare with the Pink Orchid Tree (B. monandra, PSBP-00114) elsewhere in the collection — smaller flowers, single fertile stamen vs. the multiple stamens of B. variegata.</t>
         </is>
       </c>
@@ -19708,11 +19786,10 @@
       </c>
       <c r="M114" s="32" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers - Tiny, in a compact head: a ring of white to pale-purple florets around a small dark center, on a slender stalk held just above the foliage. Blooms over a long warm season.
-Fruit - A tiny dry two-parted fruit; the plant also spreads readily by creeping stems that root at the nodes.
-Leaves - Small, opposite, ovate to spatulate, with a few teeth toward the tip.
-Form - Low, mat-forming, creeping groundcover rooting as it spreads.
+          <t>Flowers: Tiny, in a compact head: a ring of white to pale-purple florets around a small dark center, on a slender stalk held just above the foliage. Blooms over a long warm season.
+Fruit: A tiny dry two-parted fruit; the plant also spreads readily by creeping stems that root at the nodes.
+Leaves: Small, opposite, ovate to spatulate, with a few teeth toward the tip.
+Form: Low, mat-forming, creeping groundcover rooting as it spreads.
 What to Look For: A flat green mat in damp or open ground with tiny matchhead-like flowers on short stalks. Look for small butterflies working the blooms low to the ground.</t>
         </is>
       </c>
@@ -19870,11 +19947,10 @@
       </c>
       <c r="M115" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Open white to pale pink, age to deeper pink. Upper petal has a distinctive yellow and red blotch. Only one fertile stamen visible with an anther — this is the key species-level ID feature. Up to 4 inches across.
-Fruit — Flat, woody legume pods similar to B. variegata. Twist and split explosively.
-Leaves — Two-lobed, identical in form to B. variegata. The leaf alone does not distinguish the two species — use the flower stamen count.
-Form — Semi-deciduous small tree, typically 15 to 25 feet.
+          <t>Flowers: Open white to pale pink, age to deeper pink. Upper petal has a distinctive yellow and red blotch. Only one fertile stamen visible with an anther — this is the key species-level ID feature. Up to 4 inches across.
+Fruit: Flat, woody legume pods similar to B. variegata. Twist and split explosively.
+Leaves: Two-lobed, identical in form to B. variegata. The leaf alone does not distinguish the two species — use the flower stamen count.
+Form: Semi-deciduous small tree, typically 15 to 25 feet.
 What to Look For: The two-lobed leaf confirms genus. To identify species, count stamens on an open flower: one fertile stamen with a visible anther = B. monandra (this plant). Multiple stamens = B. variegata (nearby). The color progression on aging flowers — pale to deep pink with yellow-red blotch — is also distinctive.</t>
         </is>
       </c>
@@ -20027,11 +20103,10 @@
       </c>
       <c r="M116" s="32" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers - Tiny yellow composite heads, like miniature dandelions, on slender branching stems.
-Fruit - Small dry one-seeded fruits (achenes) tipped with fine white bristles, wind-dispersed.
-Leaves - In a flat basal rosette, lobed (lyre-shaped), with a larger end lobe.
-Form - Low rosette sending up thin wiry flowering stems, mostly under about 2 feet.
+          <t>Flowers: Tiny yellow composite heads, like miniature dandelions, on slender branching stems.
+Fruit: Small dry one-seeded fruits (achenes) tipped with fine white bristles, wind-dispersed.
+Leaves: In a flat basal rosette, lobed (lyre-shaped), with a larger end lobe.
+Form: Low rosette sending up thin wiry flowering stems, mostly under about 2 feet.
 What to Look For: A small rosette weed in disturbed soil and path edges, with thin stems of tiny yellow dandelion-like flowers. Easy to overlook - one of the smallest-flowered plants on the grounds.</t>
         </is>
       </c>
@@ -20181,11 +20256,10 @@
       </c>
       <c r="M117" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Small, white, in clusters. Male and female flowers on separate plants. Female flowers produce the showy fluffy white seed masses in late fall.
-Seed heads — The most recognizable feature: masses of white silky fibers on female plants in October-November, covering the plant like cotton.
-Leaves — Alternate, leathery, waxy green, with irregular toothed margins.
-Form — Evergreen to semi-evergreen shrub, 6 to 12 feet, fast growing.
+          <t>Flowers: Small, white, in clusters. Male and female flowers on separate plants. Female flowers produce the showy fluffy white seed masses in late fall.
+Seed heads: The most recognizable feature: masses of white silky fibers on female plants in October-November, covering the plant like cotton.
+Leaves: Alternate, leathery, waxy green, with irregular toothed margins.
+Form: Evergreen to semi-evergreen shrub, 6 to 12 feet, fast growing.
 What to Look For: In October-November, female plants covered in white fluffy seed masses are visible from a distance. At other times, the leathery waxy alternate leaves and the coastal setting are the markers.</t>
         </is>
       </c>
@@ -20340,10 +20414,9 @@
       </c>
       <c r="M118" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Tiny yellow composite blooms in arching plumes, October-November. The plumes are the visual signature.
-Leaves — Alternate, lance-shaped, somewhat leathery. Lower leaves larger, reducing up the stem.
-Form — Upright perennial, 2 to 5 feet, spreading by rhizomes to form colonies.
+          <t>Flowers: Tiny yellow composite blooms in arching plumes, October-November. The plumes are the visual signature.
+Leaves: Alternate, lance-shaped, somewhat leathery. Lower leaves larger, reducing up the stem.
+Form: Upright perennial, 2 to 5 feet, spreading by rhizomes to form colonies.
 What to Look For: The arching yellow flower plumes in October-November are unmistakable in their season. Year-round, the upright lance-leaved stems in a spreading colony near the coast.</t>
         </is>
       </c>
@@ -20493,12 +20566,11 @@
       </c>
       <c r="M119" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Coral-red, tubular, in terminal clusters. Attractive to hummingbirds.
-Fruit — Star-shaped capsules, coral-red, splitting to release seeds. Ornamental.
-Leaves — Deeply dissected into narrow, finger-like lobes. Medium green. The finely cut leaf is the ID signature.
-Sap — White milky latex when stems are cut or broken.
-Form — Upright shrub, 3 to 6 feet.
+          <t>Flowers: Coral-red, tubular, in terminal clusters. Attractive to hummingbirds.
+Fruit: Star-shaped capsules, coral-red, splitting to release seeds. Ornamental.
+Leaves: Deeply dissected into narrow, finger-like lobes. Medium green. The finely cut leaf is the ID signature.
+Sap: White milky latex when stems are cut or broken.
+Form: Upright shrub, 3 to 6 feet.
 What to Look For: The deeply dissected, finger-like leaf lobes are unlike most other shrubs in the collection. The coral-red flower clusters and the star-shaped fruit capsules. White sap from cut stems confirms euphorbia family membership.</t>
         </is>
       </c>
@@ -20653,11 +20725,10 @@
       </c>
       <c r="M120" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Small, white, fragrant, in flat-topped clusters. Spring bloom.
-Fruit — Small, oval, red ripening to black. In clusters. Eaten by birds.
-Leaves — Opposite, glossy dark green, ovate with a finely toothed margin. Dense, persistent.
-Form — Evergreen shrub to small tree, 10 to 20 feet. Fast growing. Dense canopy.
+          <t>Flowers: Small, white, fragrant, in flat-topped clusters. Spring bloom.
+Fruit: Small, oval, red ripening to black. In clusters. Eaten by birds.
+Leaves: Opposite, glossy dark green, ovate with a finely toothed margin. Dense, persistent.
+Form: Evergreen shrub to small tree, 10 to 20 feet. Fast growing. Dense canopy.
 What to Look For: The fragrant white flower clusters in spring are the seasonal identification feature. The glossy dark opposite leaves are the year-round marker. Compare with Walter's Viburnum (Viburnum obovatum) — native alternative with smaller leaves and similar landscape function.</t>
         </is>
       </c>
@@ -20807,11 +20878,10 @@
       </c>
       <c r="M121" s="31" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers — Inconspicuous, small, white, in spikes above the foliage. Not ornamentally significant.
-Leaves — The display. Extremely variable — leathery, in shapes from oval to strap-like to lobed. Colors include combinations of green, yellow, orange, red, and purple, with patterns from solid to blotched to veined. No two cultivars look alike.
-Sap — Milky white latex when stems or leaves are broken.
-Form — Upright evergreen shrub, 3 to 8 feet. Dense, colorful.
+          <t>Flowers: Inconspicuous, small, white, in spikes above the foliage. Not ornamentally significant.
+Leaves: The display. Extremely variable — leathery, in shapes from oval to strap-like to lobed. Colors include combinations of green, yellow, orange, red, and purple, with patterns from solid to blotched to veined. No two cultivars look alike.
+Sap: Milky white latex when stems or leaves are broken.
+Form: Upright evergreen shrub, 3 to 8 feet. Dense, colorful.
 What to Look For: The multicolored leaves are unmistakable — no other common Florida shrub produces this color range on a single leaf. The milky sap from broken stems confirms euphorbia family membership.</t>
         </is>
       </c>
@@ -21132,11 +21202,10 @@
       </c>
       <c r="M123" s="45" t="inlineStr">
         <is>
-          <t>Reproduction and Identification
-Flowers - Small, white, fragrant, in flat-topped clusters 2 to 3 inches across at the branch tips in late winter to early spring. Showy in mass.
-Fruit - A flattened drupe ripening from green to red to black through summer and fall. Eaten by birds.
-Leaves - Small, dark green, leathery, ovate to spatulate (wider near the tip), about 1 to 2 inches long, opposite, with entire or slightly toothed margins; tiny glandular dots beneath. Evergreen to tardily deciduous.
-Form - Dense, fine-textured shrub to small tree, often suckering into a thicket; takes hard pruning as a hedge.
+          <t>Flowers: Small, white, fragrant, in flat-topped clusters 2 to 3 inches across at the branch tips in late winter to early spring. Showy in mass.
+Fruit: A flattened drupe ripening from green to red to black through summer and fall. Eaten by birds.
+Leaves: Small, dark green, leathery, ovate to spatulate (wider near the tip), about 1 to 2 inches long, opposite, with entire or slightly toothed margins; tiny glandular dots beneath. Evergreen to tardily deciduous.
+Form: Dense, fine-textured shrub to small tree, often suckering into a thicket; takes hard pruning as a hedge.
 What to Look For: A dense, small-leaved shrub smothered in small white flower clusters in early spring, followed by red-to-black berries. The fine foliage and thicket habit set it apart from the larger-leaved, non-native Sweet Viburnum.</t>
         </is>
       </c>
